--- a/test_data/Dashboard/Dashboard_Test_Cases.xlsx
+++ b/test_data/Dashboard/Dashboard_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>LANDING_01</t>
+          <t>LANDING_03</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,44 +522,44 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Landing page loads after a successful login</t>
+          <t>Clicking the News nav link navigates to the News module</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>After login the app must land on the World Tax Analyzer Information workspace with the jurisdiction/category panel visible.</t>
+          <t>Clicking 'News' in the top nav must navigate to /wta/News.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Valid credentials are used to log in.</t>
+          <t>User is logged in and on the landing page.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Email: demo@reganalytics.com / Password: &lt;masked&gt;</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. Log in with valid credentials
-2. Verify the URL is /wta/Information
-3. Verify the 'Jurisdictions and Categories' panel is visible</t>
+          <t>1. Log in
+2. Click 'News' in the top navigation
+3. Verify the URL is /wta/News</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>After login the app must land on the World Tax Analyzer Information workspace with the jurisdiction/category panel visible.</t>
+          <t>Clicking 'News' in the top nav must navigate to /wta/News.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>After login the app landed on https://regplus.kaz.com.bd/wta/Information with the 'Jurisdictions and Categories' panel visible.</t>
+          <t>Clicking 'News' navigated to https://regplus.kaz.com.bd/wta/News.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[PASS] URL is /wta/Information and the Jurisdictions panel is visible</t>
+          <t>[PASS] URL contains /wta/News</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -571,7 +571,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>LANDING_02</t>
+          <t>LANDING_04</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -581,17 +581,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Top navigation and product tabs are visible</t>
+          <t>The cookie consent banner can be dismissed</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>The main module nav (Information/News/Forms/Regulations) and the product tabs (Workspace/World Tax Analyzer/Transfer Pricing Analyzer/RegBriefings) must be visible on the landing page.</t>
+          <t>The 'Please review our Terms and Conditions...' banner must disappear after clicking Accept.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on the landing page.</t>
+          <t>User is logged in; the cookie banner is showing (first session load).</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -600,124 +600,6 @@
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Verify each nav link and product tab is visible</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>The main module nav (Information/News/Forms/Regulations) and the product tabs (Workspace/World Tax Analyzer/Transfer Pricing Analyzer/RegBriefings) must be visible on the landing page.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>All main navigation links (Information, News, Forms, Regulations) and product tabs (Workspace, World Tax Analyzer, Transfer Pricing Analyzer, RegBriefings) are visible.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Information/News/Forms/Regulations links are visible
-[PASS] Workspace/World Tax Analyzer/Transfer Pricing Analyzer/RegBriefings tabs are visible</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>LANDING_03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Clicking the News nav link navigates to the News module</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'News' in the top nav must navigate to /wta/News.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Click 'News' in the top navigation
-3. Verify the URL is /wta/News</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'News' in the top nav must navigate to /wta/News.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'News' navigated to https://regplus.kaz.com.bd/wta/News.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] URL contains /wta/News</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>LANDING_04</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>The cookie consent banner can be dismissed</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>The 'Please review our Terms and Conditions...' banner must disappear after clicking Accept.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in; the cookie banner is showing (first session load).</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Verify the cookie banner is visible
@@ -725,19 +607,137 @@
 4. Verify the banner is no longer visible</t>
         </is>
       </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>The 'Please review our Terms and Conditions...' banner must disappear after clicking Accept.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Clicking Accept dismissed the cookie banner.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Cookie banner is no longer visible after Accept</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_05</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Selecting a jurisdiction checks its checkbox</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Clicking a country in the Jurisdictions panel (e.g. Australia) must check its checkbox, confirming the left panel is interactive.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page, Asia Pacific region selected by default.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click the 'Australia' checkbox in the Jurisdictions panel
+3. Verify the checkbox becomes checked</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Clicking a country in the Jurisdictions panel (e.g. Australia) must check its checkbox, confirming the left panel is interactive.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Australia' in the Jurisdictions panel checked its checkbox, confirming the panel responds to selection.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Australia's checkbox is checked after clicking it</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_06</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the Forms nav link navigates to the Forms module</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Forms' in the top nav must navigate to /wta/Forms.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click 'Forms' in the top navigation
+3. Verify the URL is /wta/Forms</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>The 'Please review our Terms and Conditions...' banner must disappear after clicking Accept.</t>
+          <t>Clicking 'Forms' in the top nav must navigate to /wta/Forms.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Clicking Accept dismissed the cookie banner.</t>
+          <t>Clicking 'Forms' navigated to https://regplus.kaz.com.bd/wta/Forms.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Cookie banner is no longer visible after Accept</t>
+          <t>[PASS] URL contains /wta/Forms</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>LANDING_05</t>
+          <t>LANDING_07</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -759,47 +759,1878 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Selecting a jurisdiction checks its checkbox</t>
+          <t>Clicking the Regulations nav link navigates to the Regulations module</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Clicking a country in the Jurisdictions panel (e.g. Australia) must check its checkbox, confirming the left panel is interactive.</t>
+          <t>Clicking 'Regulations' in the top nav must navigate to /wta/Regulations.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on the landing page, Asia Pacific region selected by default.</t>
+          <t>User is logged in and on the landing page.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click 'Regulations' in the top navigation
+3. Verify the URL is /wta/Regulations</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Regulations' in the top nav must navigate to /wta/Regulations.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Regulations' navigated to https://regplus.kaz.com.bd/wta/Regulations.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] URL contains /wta/Regulations</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_10</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Switching to the Americas region tab swaps the country list</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Americas' must show Americas countries (e.g. Brazil) and hide Asia Pacific countries (e.g. Australia).</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page, Asia Pacific selected by default.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click the 'Americas' region tab
+3. Verify Brazil is shown and Australia is hidden</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Americas' must show Americas countries (e.g. Brazil) and hide Asia Pacific countries (e.g. Australia).</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Switching to Americas correctly swapped the country list.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Brazil (Americas) is visible and Australia (Asia Pacific) is not</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_11</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Switching to the Europe region tab swaps the country list</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Europe' must show Europe countries (e.g. France) and hide Asia Pacific countries (e.g. Australia).</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click the 'Europe' region tab
+3. Verify France is shown and Australia is hidden</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Europe' must show Europe countries (e.g. France) and hide Asia Pacific countries (e.g. Australia).</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Switching to Europe correctly swapped the country list.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] France (Europe) is visible and Australia (Asia Pacific) is not</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_12</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Switching to the MEA region tab swaps the country list</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'MEA' must show MEA countries (e.g. Egypt) and hide Asia Pacific countries (e.g. Australia).</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click the 'MEA' region tab
+3. Verify Egypt is shown and Australia is hidden</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'MEA' must show MEA countries (e.g. Egypt) and hide Asia Pacific countries (e.g. Australia).</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Switching to MEA correctly swapped the country list.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Egypt (MEA) is visible and Australia (Asia Pacific) is not</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_13</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Clicking a region tab activates it and deactivates the previous one</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>After clicking 'Americas', it must carry the active/selected styling and 'Asia Pacific' must no longer carry it.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page, Asia Pacific active by default.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click the 'Americas' region tab
+3. Verify Americas is now active and Asia Pacific is not</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>After clicking 'Americas', it must carry the active/selected styling and 'Asia Pacific' must no longer carry it.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Americas' correctly toggled the active region tab.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Americas' is now active and 'Asia Pacific' is not</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_14</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Searching countries filters the jurisdiction checklist</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Typing 'Austra' in the country search box must show Australia and hide non-matching countries (e.g. Bangladesh).</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page, Asia Pacific region active.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Search term: Austra</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Type 'Austra' into the country search box
+3. Verify Australia is shown and Bangladesh is hidden</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Typing 'Austra' in the country search box must show Australia and hide non-matching countries (e.g. Bangladesh).</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Searching 'Austra' correctly filtered the country list.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Australia is shown and Bangladesh is hidden after searching 'Austra'</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_15</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Country search is case-insensitive</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Typing a lowercase search term ('austra') must still match 'Australia'.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Search term: austra (lowercase)</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Type 'austra' (lowercase) into the country search box
+3. Verify Australia is still shown</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Typing a lowercase search term ('austra') must still match 'Australia'.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Country search is case-insensitive: 'austra' matched Australia.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Australia is shown for the lowercase search 'austra'</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_16</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Searching for a non-existent country shows a 'no results' message</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Typing a term that matches no country must show 'No countries found matching "&lt;term&gt;"'.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Search term: zzzznotreal</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Type 'zzzznotreal' into the country search box
+3. Verify the 'No countries found matching...' message appears</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Typing a term that matches no country must show 'No countries found matching "&lt;term&gt;"'.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>The 'No countries found matching...' empty-state message correctly appeared.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'No countries found matching...' message is shown</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_17</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Clearing the country search box restores the full list</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>After filtering to 'Austra' and then clearing the search box, the full country list (including Bangladesh) must reappear.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Search 'Austra'
+3. Clear the search box
+4. Verify Bangladesh reappears</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>After filtering to 'Austra' and then clearing the search box, the full country list (including Bangladesh) must reappear.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Clearing the country search box correctly restored the full country list.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Bangladesh reappears after clearing the country search</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_18</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Searching categories filters the category tree</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Typing 'Liability' in the category search box must show 'Liability to Tax' and hide non-matching categories (e.g. 'Tax Compliance').</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Search term: Liability</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Type 'Liability' into the category search box
+3. Verify 'Liability to Tax' is shown and 'Tax Compliance' is hidden</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Typing 'Liability' in the category search box must show 'Liability to Tax' and hide non-matching categories (e.g. 'Tax Compliance').</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Searching 'Liability' correctly filtered the category tree.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Liability to Tax' is shown and 'Tax Compliance' is hidden after searching 'Liability'</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_19</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Searching for a non-existent category shows 'No results found.'</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Typing a term that matches no category must show 'No results found.' - note this wording differs from the country search's empty state, which echoes the search term.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Search term: zzznotreal</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Type 'zzznotreal' into the category search box
+3. Verify 'No results found.' appears</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Typing a term that matches no category must show 'No results found.' - note this wording differs from the country search's empty state, which echoes the search term.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>The 'No results found.' empty-state message correctly appeared for the category search.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'No results found.' message is shown</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_20</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Clearing the category search box restores the full tree</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>After filtering to 'Liability' and then clearing the search box, the full category tree (including 'Tax Compliance') must reappear.</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Search 'Liability'
+3. Clear the search box
+4. Verify 'Tax Compliance' reappears</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>After filtering to 'Liability' and then clearing the search box, the full category tree (including 'Tax Compliance') must reappear.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Clearing the category search box correctly restored the full category tree.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Tax Compliance' reappears after clearing the category search</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_22</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>'Check All' checks every top-level category</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Check All' must check every top-level category, e.g. 'Liability to Tax'.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page, 'Check All' unchecked.</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click 'Check All'
+3. Verify 'Liability to Tax' becomes checked</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Check All' must check every top-level category, e.g. 'Liability to Tax'.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Check All' correctly cascaded to check every top-level category.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Check All' and 'Liability to Tax' are both checked after clicking 'Check All'</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_23</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Unchecking 'Check All' unchecks every category again</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>After checking 'Check All', clicking it again must uncheck every category, e.g. 'Liability to Tax'.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click 'Check All' to check it
+3. Click 'Check All' again to uncheck it
+4. Verify 'Liability to Tax' is unchecked</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>After checking 'Check All', clicking it again must uncheck every category, e.g. 'Liability to Tax'.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Toggling 'Check All' off correctly unchecked every category.</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Check All' and 'Liability to Tax' are both unchecked after toggling 'Check All' off</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_24</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Depth control expands the visible category tree</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Clicking Depth level '4' must reveal substantially more nested category content than the default view (confirmed live: default/1 ~585 characters of panel text vs. depth 4 ~3519 characters).</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Depth level: 4</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Record the category panel's text length
+3. Click Depth '4'
+4. Verify the panel's text length increased substantially</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Clicking Depth level '4' must reveal substantially more nested category content than the default view (confirmed live: default/1 ~585 characters of panel text vs. depth 4 ~3519 characters).</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Selecting Depth '4' expanded the category panel from 585 to 3519 characters of visible content.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Category panel text length roughly doubles or more after selecting Depth 4</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_25</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Selecting a second country keeps the first one checked</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Checking 'Australia' then 'Bangladesh' must leave both checked - the jurisdiction panel supports multi-select.</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Countries: Australia, Bangladesh</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Check 'Australia'
+3. Check 'Bangladesh'
+4. Verify both remain checked</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Checking 'Australia' then 'Bangladesh' must leave both checked - the jurisdiction panel supports multi-select.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>The jurisdiction panel correctly supports multi-select: both Australia and Bangladesh remained checked.</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Both 'Australia' and 'Bangladesh' remain checked (multi-select)</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Deselecting a checked country unchecks it</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Checking then re-clicking 'Australia' must uncheck it.</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>Country: Australia</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Click the 'Australia' checkbox in the Jurisdictions panel
-3. Verify the checkbox becomes checked</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Clicking a country in the Jurisdictions panel (e.g. Australia) must check its checkbox, confirming the left panel is interactive.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Australia' in the Jurisdictions panel checked its checkbox, confirming the panel responds to selection.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Australia's checkbox is checked after clicking it</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Check 'Australia'
+3. Click 'Australia' again to uncheck it
+4. Verify it is unchecked</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Checking then re-clicking 'Australia' must uncheck it.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Australia' a second time correctly unchecked it.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Australia' is unchecked after clicking it a second time</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_27</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>'Workspace' product tab navigates to the Companydata dashboard</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the 'Workspace' tab must navigate to /companydata/dashboard/ - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click the 'Workspace' tab
+3. Verify the URL is /companydata/dashboard/</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the 'Workspace' tab must navigate to /companydata/dashboard/ - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Workspace' navigated to https://regplus.kaz.com.bd/companydata/dashboard/, the Companydata dashboard.</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] URL contains /companydata/dashboard/</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_28</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>'Transfer Pricing Analyzer' tab navigates to the TPA module</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the 'Transfer Pricing Analyzer' tab must navigate to /tpa/Home - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click the 'Transfer Pricing Analyzer' tab
+3. Verify the URL is /tpa/Home</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the 'Transfer Pricing Analyzer' tab must navigate to /tpa/Home - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Transfer Pricing Analyzer' navigated to https://regplus.kaz.com.bd/tpa/Home.</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] URL contains /tpa/Home</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_29</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>'RegBriefings' tab navigates to the RegBriefings module</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the 'RegBriefings' tab must navigate to /regbrief/home/ - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click the 'RegBriefings' tab
+3. Verify the URL contains /regbrief/home/</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the 'RegBriefings' tab must navigate to /regbrief/home/ - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'RegBriefings' navigated to https://regplus.kaz.com.bd/regbrief/home/myBriefings.</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] URL contains /regbrief/home/</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_30</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Browser back navigation returns from News to Information</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>After navigating to News via the top nav, using the browser's back button must return to /wta/Information.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click 'News'
+3. Go back
+4. Verify the URL is /wta/Information</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>After navigating to News via the top nav, using the browser's back button must return to /wta/Information.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Browser back correctly returned to https://regplus.kaz.com.bd/wta/Information.</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Browser back returns to /wta/Information</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_31</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Reloading the page preserves the authenticated session</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Reloading /wta/Information (F5) must keep the user authenticated and on the same page, not bounce them to the login page.</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Reload the page
+3. Verify the user is still on /wta/Information, not redirected to /auth/login</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Reloading /wta/Information (F5) must keep the user authenticated and on the same page, not bounce them to the login page.</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Reloading the page correctly preserved the authenticated session; still on https://regplus.kaz.com.bd/wta/Information.</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] User remains on /wta/Information after reload (not redirected to login)</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_33</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Exactly 4 region tabs are present</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>The jurisdiction panel must show exactly 4 region tabs: Asia Pacific, Americas, Europe, MEA - no more, no fewer.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify exactly 4 region tabs are present</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>The jurisdiction panel must show exactly 4 region tabs: Asia Pacific, Americas, Europe, MEA - no more, no fewer.</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Exactly the 4 expected region tabs (Asia Pacific, Americas, Europe, MEA) are present.</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Each of the 4 region tabs appears exactly once</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_34</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Asia Pacific region shows the expected number of countries</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>The Asia Pacific region (default) must list 25 countries, confirmed live (Australia through Vietnam).</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page, Asia Pacific active.</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Count the visible country checkboxes in the Asia Pacific list
+3. Verify the count is 25</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>The Asia Pacific region (default) must list 25 countries, confirmed live (Australia through Vietnam).</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Asia Pacific correctly lists 25 countries.</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Asia Pacific lists exactly 25 countries</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_35</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Exactly the 5 expected main nav items are present</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>The top nav must show Information, Pillar 2, News, Forms and Regulations - no more, no fewer.</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify each of the 5 main nav items appears exactly once</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>The top nav must show Information, Pillar 2, News, Forms and Regulations - no more, no fewer.</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Exactly the 5 expected main nav items are present.</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Each of the 5 main nav items appears exactly once</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_36</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Expected top-level categories are present in the tree</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>The category tree's default view must include the top-level categories 'Liability to Tax' and 'Tax Compliance'.</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify 'Liability to Tax' and 'Tax Compliance' are visible</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>The category tree's default view must include the top-level categories 'Liability to Tax' and 'Tax Compliance'.</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Both expected top-level categories are visible in the default tree view.</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Liability to Tax' and 'Tax Compliance' are both visible</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_37</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Exactly 4 product tabs are present</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>The product-tab row must show Workspace, World Tax Analyzer, Transfer Pricing Analyzer and RegBriefings - no more, no fewer.</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify each of the 4 product tabs appears exactly once</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>The product-tab row must show Workspace, World Tax Analyzer, Transfer Pricing Analyzer and RegBriefings - no more, no fewer.</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Exactly the 4 expected product tabs are present.</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Each of the 4 product tabs appears exactly once</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_38</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>A single category can be checked without using 'Check All'</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Liability to Tax's checkbox directly must check it, while 'Check All' remains unchecked (it only reflects when every category is checked). Note: the category LABEL text has no 'for' attribute linking it to its checkbox (confirmed live) - clicking the label is a no-op; only the checkbox input itself (or 'Check All', which has its own working handler) toggles selection.</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Category: Liability to Tax</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click 'Liability to Tax's checkbox
+3. Verify it is checked and 'Check All' remains unchecked</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Liability to Tax's checkbox directly must check it, while 'Check All' remains unchecked (it only reflects when every category is checked). Note: the category LABEL text has no 'for' attribute linking it to its checkbox (confirmed live) - clicking the label is a no-op; only the checkbox input itself (or 'Check All', which has its own working handler) toggles selection.</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>A single category can be selected independently of 'Check All'.</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Liability to Tax' is checked while 'Check All' remains unchecked</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_39</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Special-character input in the country search doesn't error</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Typing special characters into the country search box must be handled gracefully (the same 'No countries found...' empty state, no crash).</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Search term: @@@###$$$</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Type '@@@###$$$' into the country search box
+3. Verify the page does not error and shows the no-match message</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Typing special characters into the country search box must be handled gracefully (the same 'No countries found...' empty state, no crash).</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Special-character input was handled gracefully with the expected empty-state message.</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Special-character search shows the no-match message without breaking the panel</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_40</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Special-character input in the category search doesn't error</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Typing special characters into the category search box must be handled gracefully (the same 'No results found.' empty state, no crash).</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Search term: @@@###$$$</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Type '@@@###$$$' into the category search box
+3. Verify the page does not error and shows 'No results found.'</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Typing special characters into the category search box must be handled gracefully (the same 'No results found.' empty state, no crash).</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Special-character input was handled gracefully with the expected empty-state message.</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Special-character search shows 'No results found.' without breaking the panel</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_41</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>'World Tax Analyzer' tab keeps the user within WTA</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the already-active 'World Tax Analyzer' product tab must not navigate away from the WTA module.</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page (WTA already active).</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click the 'World Tax Analyzer' tab
+3. Verify the URL is still within /wta/</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the already-active 'World Tax Analyzer' product tab must not navigate away from the WTA module.</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the already-active 'World Tax Analyzer' tab correctly kept the user within WTA, at https://regplus.kaz.com.bd/wta/Information.</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] URL remains within /wta/ after clicking the already-active tab</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_42</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>'Information' nav link points to /wta/Information</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>The 'Information' nav link's href must point to /wta/Information, consistent with it being the post-login landing page.</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify the 'Information' nav link's href</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>The 'Information' nav link's href must point to /wta/Information, consistent with it being the post-login landing page.</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>'Information' nav link correctly points to /wta/Information.</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Information' nav link href contains /wta/Information</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/Dashboard/Dashboard_Test_Cases.xlsx
+++ b/test_data/Dashboard/Dashboard_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,94 +512,212 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>LANDING_01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Landing page loads after a successful login</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>After login the app must land on the World Tax Analyzer Information workspace with the jurisdiction/category panel visible.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Valid credentials are used to log in.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Email: demo@reganalytics.com / Password: &lt;masked&gt;</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in with valid credentials
+2. Verify the URL is /wta/Information
+3. Verify the 'Jurisdictions and Categories' panel is visible</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>After login the app must land on the World Tax Analyzer Information workspace with the jurisdiction/category panel visible.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>After login the app landed on https://regplus.kaz.com.bd/wta/Information with the 'Jurisdictions and Categories' panel visible.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] URL is /wta/Information and the Jurisdictions panel is visible</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Top navigation and product tabs are visible</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>The main module nav (Information/News/Forms/Regulations) and the product tabs (Workspace/World Tax Analyzer/Transfer Pricing Analyzer/RegBriefings) must be visible on the landing page.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify each nav link and product tab is visible</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>The main module nav (Information/News/Forms/Regulations) and the product tabs (Workspace/World Tax Analyzer/Transfer Pricing Analyzer/RegBriefings) must be visible on the landing page.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>All main navigation links (Information, News, Forms, Regulations) and product tabs (Workspace, World Tax Analyzer, Transfer Pricing Analyzer, RegBriefings) are visible.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Information/News/Forms/Regulations links are visible
+[PASS] Workspace/World Tax Analyzer/Transfer Pricing Analyzer/RegBriefings tabs are visible</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
           <t>LANDING_03</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Clicking the News nav link navigates to the News module</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Clicking 'News' in the top nav must navigate to /wta/News.</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click 'News' in the top navigation
 3. Verify the URL is /wta/News</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Clicking 'News' in the top nav must navigate to /wta/News.</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Clicking 'News' navigated to https://regplus.kaz.com.bd/wta/News.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>[PASS] URL contains /wta/News</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>LANDING_04</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>The cookie consent banner can be dismissed</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>The 'Please review our Terms and Conditions...' banner must disappear after clicking Accept.</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>User is logged in; the cookie banner is showing (first session load).</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Verify the cookie banner is visible
@@ -607,649 +725,765 @@
 4. Verify the banner is no longer visible</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>The 'Please review our Terms and Conditions...' banner must disappear after clicking Accept.</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Clicking Accept dismissed the cookie banner.</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>[PASS] Cookie banner is no longer visible after Accept</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>LANDING_05</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Selecting a jurisdiction checks its checkbox</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Clicking a country in the Jurisdictions panel (e.g. Australia) must check its checkbox, confirming the left panel is interactive.</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on the landing page, Asia Pacific region selected by default.</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Country: Australia</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click the 'Australia' checkbox in the Jurisdictions panel
 3. Verify the checkbox becomes checked</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Clicking a country in the Jurisdictions panel (e.g. Australia) must check its checkbox, confirming the left panel is interactive.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Australia' in the Jurisdictions panel checked its checkbox, confirming the panel responds to selection.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>[PASS] Australia's checkbox is checked after clicking it</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>LANDING_06</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Clicking the Forms nav link navigates to the Forms module</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Forms' in the top nav must navigate to /wta/Forms.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click 'Forms' in the top navigation
 3. Verify the URL is /wta/Forms</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Forms' in the top nav must navigate to /wta/Forms.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Forms' navigated to https://regplus.kaz.com.bd/wta/Forms.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>[PASS] URL contains /wta/Forms</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>LANDING_07</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Clicking the Regulations nav link navigates to the Regulations module</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Regulations' in the top nav must navigate to /wta/Regulations.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click 'Regulations' in the top navigation
 3. Verify the URL is /wta/Regulations</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Regulations' in the top nav must navigate to /wta/Regulations.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Regulations' navigated to https://regplus.kaz.com.bd/wta/Regulations.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>[PASS] URL contains /wta/Regulations</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>'Pillar 2' nav button is visible and enabled</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>The 'Pillar 2' dropdown trigger in the top nav must be visible and enabled. Its dropdown contents are covered in depth by the WTA Pillar2 Menu module - this is a light presence check only, to avoid duplicating that coverage.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify the 'Pillar 2' nav button is visible and enabled</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>The 'Pillar 2' dropdown trigger in the top nav must be visible and enabled. Its dropdown contents are covered in depth by the WTA Pillar2 Menu module - this is a light presence check only, to avoid duplicating that coverage.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>The 'Pillar 2' nav button is visible and enabled.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Pillar 2' nav button is visible and enabled</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>'Asia Pacific' region tab is selected by default</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>On first load, the 'Asia Pacific' region tab must carry the active/selected styling and 'Americas' must not.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify 'Asia Pacific' is the active region tab</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>On first load, the 'Asia Pacific' region tab must carry the active/selected styling and 'Americas' must not.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>'Asia Pacific' is the default active region tab.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Asia Pacific' is active and 'Americas' is not, by default</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>LANDING_10</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Switching to the Americas region tab swaps the country list</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Americas' must show Americas countries (e.g. Brazil) and hide Asia Pacific countries (e.g. Australia).</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on the landing page, Asia Pacific selected by default.</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click the 'Americas' region tab
 3. Verify Brazil is shown and Australia is hidden</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Americas' must show Americas countries (e.g. Brazil) and hide Asia Pacific countries (e.g. Australia).</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Switching to Americas correctly swapped the country list.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>[PASS] Brazil (Americas) is visible and Australia (Asia Pacific) is not</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>LANDING_11</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Switching to the Europe region tab swaps the country list</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Europe' must show Europe countries (e.g. France) and hide Asia Pacific countries (e.g. Australia).</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click the 'Europe' region tab
 3. Verify France is shown and Australia is hidden</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Europe' must show Europe countries (e.g. France) and hide Asia Pacific countries (e.g. Australia).</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Switching to Europe correctly swapped the country list.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>[PASS] France (Europe) is visible and Australia (Asia Pacific) is not</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>LANDING_12</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Switching to the MEA region tab swaps the country list</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Clicking 'MEA' must show MEA countries (e.g. Egypt) and hide Asia Pacific countries (e.g. Australia).</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click the 'MEA' region tab
 3. Verify Egypt is shown and Australia is hidden</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Clicking 'MEA' must show MEA countries (e.g. Egypt) and hide Asia Pacific countries (e.g. Australia).</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>Switching to MEA correctly swapped the country list.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>[PASS] Egypt (MEA) is visible and Australia (Asia Pacific) is not</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>LANDING_13</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Clicking a region tab activates it and deactivates the previous one</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>After clicking 'Americas', it must carry the active/selected styling and 'Asia Pacific' must no longer carry it.</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on the landing page, Asia Pacific active by default.</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click the 'Americas' region tab
 3. Verify Americas is now active and Asia Pacific is not</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>After clicking 'Americas', it must carry the active/selected styling and 'Asia Pacific' must no longer carry it.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Americas' correctly toggled the active region tab.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Americas' is now active and 'Asia Pacific' is not</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>LANDING_14</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Searching countries filters the jurisdiction checklist</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Typing 'Austra' in the country search box must show Australia and hide non-matching countries (e.g. Bangladesh).</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on the landing page, Asia Pacific region active.</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Search term: Austra</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Type 'Austra' into the country search box
 3. Verify Australia is shown and Bangladesh is hidden</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Typing 'Austra' in the country search box must show Australia and hide non-matching countries (e.g. Bangladesh).</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>Searching 'Austra' correctly filtered the country list.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>[PASS] Australia is shown and Bangladesh is hidden after searching 'Austra'</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>LANDING_15</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Country search is case-insensitive</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Typing a lowercase search term ('austra') must still match 'Australia'.</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Search term: austra (lowercase)</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Type 'austra' (lowercase) into the country search box
 3. Verify Australia is still shown</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Typing a lowercase search term ('austra') must still match 'Australia'.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>Country search is case-insensitive: 'austra' matched Australia.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>[PASS] Australia is shown for the lowercase search 'austra'</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>LANDING_16</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Searching for a non-existent country shows a 'no results' message</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Typing a term that matches no country must show 'No countries found matching "&lt;term&gt;"'.</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Search term: zzzznotreal</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Type 'zzzznotreal' into the country search box
 3. Verify the 'No countries found matching...' message appears</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Typing a term that matches no country must show 'No countries found matching "&lt;term&gt;"'.</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>The 'No countries found matching...' empty-state message correctly appeared.</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'No countries found matching...' message is shown</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>LANDING_17</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Clearing the country search box restores the full list</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>After filtering to 'Austra' and then clearing the search box, the full country list (including Bangladesh) must reappear.</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Search 'Austra'
@@ -1257,177 +1491,177 @@
 4. Verify Bangladesh reappears</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>After filtering to 'Austra' and then clearing the search box, the full country list (including Bangladesh) must reappear.</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>Clearing the country search box correctly restored the full country list.</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>[PASS] Bangladesh reappears after clearing the country search</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>LANDING_18</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Searching categories filters the category tree</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Typing 'Liability' in the category search box must show 'Liability to Tax' and hide non-matching categories (e.g. 'Tax Compliance').</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Search term: Liability</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Type 'Liability' into the category search box
 3. Verify 'Liability to Tax' is shown and 'Tax Compliance' is hidden</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Typing 'Liability' in the category search box must show 'Liability to Tax' and hide non-matching categories (e.g. 'Tax Compliance').</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>Searching 'Liability' correctly filtered the category tree.</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Liability to Tax' is shown and 'Tax Compliance' is hidden after searching 'Liability'</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>LANDING_19</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Searching for a non-existent category shows 'No results found.'</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Typing a term that matches no category must show 'No results found.' - note this wording differs from the country search's empty state, which echoes the search term.</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Search term: zzznotreal</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Type 'zzznotreal' into the category search box
 3. Verify 'No results found.' appears</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Typing a term that matches no category must show 'No results found.' - note this wording differs from the country search's empty state, which echoes the search term.</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>The 'No results found.' empty-state message correctly appeared for the category search.</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'No results found.' message is shown</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>LANDING_20</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Clearing the category search box restores the full tree</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>After filtering to 'Liability' and then clearing the search box, the full category tree (including 'Tax Compliance') must reappear.</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Search 'Liability'
@@ -1435,118 +1669,176 @@
 4. Verify 'Tax Compliance' reappears</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>After filtering to 'Liability' and then clearing the search box, the full category tree (including 'Tax Compliance') must reappear.</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>Clearing the category search box correctly restored the full category tree.</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Tax Compliance' reappears after clearing the category search</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_21</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>'Check All' (categories) is unchecked by default</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>On first load, the 'Check All' category checkbox must be unchecked.</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify the 'Check All' checkbox is unchecked</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>On first load, the 'Check All' category checkbox must be unchecked.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>'Check All' is unchecked by default, as expected.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Check All' checkbox is unchecked by default</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>LANDING_22</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>'Check All' checks every top-level category</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Check All' must check every top-level category, e.g. 'Liability to Tax'.</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on the landing page, 'Check All' unchecked.</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click 'Check All'
 3. Verify 'Liability to Tax' becomes checked</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Check All' must check every top-level category, e.g. 'Liability to Tax'.</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Check All' correctly cascaded to check every top-level category.</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Check All' and 'Liability to Tax' are both checked after clicking 'Check All'</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>LANDING_23</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Unchecking 'Check All' unchecks every category again</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>After checking 'Check All', clicking it again must uncheck every category, e.g. 'Liability to Tax'.</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click 'Check All' to check it
@@ -1554,59 +1846,59 @@
 4. Verify 'Liability to Tax' is unchecked</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>After checking 'Check All', clicking it again must uncheck every category, e.g. 'Liability to Tax'.</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>Toggling 'Check All' off correctly unchecked every category.</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Check All' and 'Liability to Tax' are both unchecked after toggling 'Check All' off</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>LANDING_24</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Depth control expands the visible category tree</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Clicking Depth level '4' must reveal substantially more nested category content than the default view (confirmed live: default/1 ~585 characters of panel text vs. depth 4 ~3519 characters).</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Depth level: 4</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Record the category panel's text length
@@ -1614,59 +1906,59 @@
 4. Verify the panel's text length increased substantially</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Clicking Depth level '4' must reveal substantially more nested category content than the default view (confirmed live: default/1 ~585 characters of panel text vs. depth 4 ~3519 characters).</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>Selecting Depth '4' expanded the category panel from 585 to 3519 characters of visible content.</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>[PASS] Category panel text length roughly doubles or more after selecting Depth 4</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>LANDING_25</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Selecting a second country keeps the first one checked</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Checking 'Australia' then 'Bangladesh' must leave both checked - the jurisdiction panel supports multi-select.</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Countries: Australia, Bangladesh</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Check 'Australia'
@@ -1674,59 +1966,59 @@
 4. Verify both remain checked</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Checking 'Australia' then 'Bangladesh' must leave both checked - the jurisdiction panel supports multi-select.</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>The jurisdiction panel correctly supports multi-select: both Australia and Bangladesh remained checked.</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>[PASS] Both 'Australia' and 'Bangladesh' remain checked (multi-select)</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>LANDING_26</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Deselecting a checked country unchecks it</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Checking then re-clicking 'Australia' must uncheck it.</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Country: Australia</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Check 'Australia'
@@ -1734,236 +2026,236 @@
 4. Verify it is unchecked</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Checking then re-clicking 'Australia' must uncheck it.</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Australia' a second time correctly unchecked it.</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Australia' is unchecked after clicking it a second time</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>LANDING_27</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>'Workspace' product tab navigates to the Companydata dashboard</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Clicking the 'Workspace' tab must navigate to /companydata/dashboard/ - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click the 'Workspace' tab
 3. Verify the URL is /companydata/dashboard/</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Clicking the 'Workspace' tab must navigate to /companydata/dashboard/ - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Workspace' navigated to https://regplus.kaz.com.bd/companydata/dashboard/, the Companydata dashboard.</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>[PASS] URL contains /companydata/dashboard/</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>LANDING_28</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>'Transfer Pricing Analyzer' tab navigates to the TPA module</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Clicking the 'Transfer Pricing Analyzer' tab must navigate to /tpa/Home - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click the 'Transfer Pricing Analyzer' tab
 3. Verify the URL is /tpa/Home</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Clicking the 'Transfer Pricing Analyzer' tab must navigate to /tpa/Home - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Transfer Pricing Analyzer' navigated to https://regplus.kaz.com.bd/tpa/Home.</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>[PASS] URL contains /tpa/Home</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>LANDING_29</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>'RegBriefings' tab navigates to the RegBriefings module</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Clicking the 'RegBriefings' tab must navigate to /regbrief/home/ - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click the 'RegBriefings' tab
 3. Verify the URL contains /regbrief/home/</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Clicking the 'RegBriefings' tab must navigate to /regbrief/home/ - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>Clicking 'RegBriefings' navigated to https://regplus.kaz.com.bd/regbrief/home/myBriefings.</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>[PASS] URL contains /regbrief/home/</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>LANDING_30</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Browser back navigation returns from News to Information</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>After navigating to News via the top nav, using the browser's back button must return to /wta/Information.</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click 'News'
@@ -1971,666 +2263,724 @@
 4. Verify the URL is /wta/Information</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>After navigating to News via the top nav, using the browser's back button must return to /wta/Information.</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>Browser back correctly returned to https://regplus.kaz.com.bd/wta/Information.</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>[PASS] Browser back returns to /wta/Information</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>LANDING_31</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Reloading the page preserves the authenticated session</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Reloading /wta/Information (F5) must keep the user authenticated and on the same page, not bounce them to the login page.</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Reload the page
 3. Verify the user is still on /wta/Information, not redirected to /auth/login</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Reloading /wta/Information (F5) must keep the user authenticated and on the same page, not bounce them to the login page.</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>Reloading the page correctly preserved the authenticated session; still on https://regplus.kaz.com.bd/wta/Information.</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>[PASS] User remains on /wta/Information after reload (not redirected to login)</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_32</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>The content placeholder is shown before any selection</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Before selecting a jurisdiction or category, the right panel must show 'Select Jurisdictions and Categories'.</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page, nothing selected.</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify the 'Select Jurisdictions and Categories' placeholder is visible</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Before selecting a jurisdiction or category, the right panel must show 'Select Jurisdictions and Categories'.</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>The 'Select Jurisdictions and Categories' placeholder is correctly shown before any selection.</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Placeholder text is visible before any selection</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>LANDING_33</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Exactly 4 region tabs are present</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>The jurisdiction panel must show exactly 4 region tabs: Asia Pacific, Americas, Europe, MEA - no more, no fewer.</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Verify exactly 4 region tabs are present</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>The jurisdiction panel must show exactly 4 region tabs: Asia Pacific, Americas, Europe, MEA - no more, no fewer.</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>Exactly the 4 expected region tabs (Asia Pacific, Americas, Europe, MEA) are present.</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>[PASS] Each of the 4 region tabs appears exactly once</t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>LANDING_34</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Asia Pacific region shows the expected number of countries</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>The Asia Pacific region (default) must list 25 countries, confirmed live (Australia through Vietnam).</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on the landing page, Asia Pacific active.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Count the visible country checkboxes in the Asia Pacific list
 3. Verify the count is 25</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>The Asia Pacific region (default) must list 25 countries, confirmed live (Australia through Vietnam).</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>Asia Pacific correctly lists 25 countries.</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>[PASS] Asia Pacific lists exactly 25 countries</t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>LANDING_35</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Exactly the 5 expected main nav items are present</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>The top nav must show Information, Pillar 2, News, Forms and Regulations - no more, no fewer.</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Verify each of the 5 main nav items appears exactly once</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>The top nav must show Information, Pillar 2, News, Forms and Regulations - no more, no fewer.</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>Exactly the 5 expected main nav items are present.</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>[PASS] Each of the 5 main nav items appears exactly once</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>LANDING_36</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Expected top-level categories are present in the tree</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>The category tree's default view must include the top-level categories 'Liability to Tax' and 'Tax Compliance'.</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Verify 'Liability to Tax' and 'Tax Compliance' are visible</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>The category tree's default view must include the top-level categories 'Liability to Tax' and 'Tax Compliance'.</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>Both expected top-level categories are visible in the default tree view.</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Liability to Tax' and 'Tax Compliance' are both visible</t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>LANDING_37</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Exactly 4 product tabs are present</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>The product-tab row must show Workspace, World Tax Analyzer, Transfer Pricing Analyzer and RegBriefings - no more, no fewer.</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Verify each of the 4 product tabs appears exactly once</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>The product-tab row must show Workspace, World Tax Analyzer, Transfer Pricing Analyzer and RegBriefings - no more, no fewer.</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>Exactly the 4 expected product tabs are present.</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>[PASS] Each of the 4 product tabs appears exactly once</t>
         </is>
       </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>LANDING_38</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>A single category can be checked without using 'Check All'</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Liability to Tax's checkbox directly must check it, while 'Check All' remains unchecked (it only reflects when every category is checked). Note: the category LABEL text has no 'for' attribute linking it to its checkbox (confirmed live) - clicking the label is a no-op; only the checkbox input itself (or 'Check All', which has its own working handler) toggles selection.</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Category: Liability to Tax</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click 'Liability to Tax's checkbox
 3. Verify it is checked and 'Check All' remains unchecked</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Liability to Tax's checkbox directly must check it, while 'Check All' remains unchecked (it only reflects when every category is checked). Note: the category LABEL text has no 'for' attribute linking it to its checkbox (confirmed live) - clicking the label is a no-op; only the checkbox input itself (or 'Check All', which has its own working handler) toggles selection.</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>A single category can be selected independently of 'Check All'.</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Liability to Tax' is checked while 'Check All' remains unchecked</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>LANDING_39</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Special-character input in the country search doesn't error</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Typing special characters into the country search box must be handled gracefully (the same 'No countries found...' empty state, no crash).</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Search term: @@@###$$$</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Type '@@@###$$$' into the country search box
 3. Verify the page does not error and shows the no-match message</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Typing special characters into the country search box must be handled gracefully (the same 'No countries found...' empty state, no crash).</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>Special-character input was handled gracefully with the expected empty-state message.</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>[PASS] Special-character search shows the no-match message without breaking the panel</t>
         </is>
       </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>LANDING_40</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Special-character input in the category search doesn't error</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Typing special characters into the category search box must be handled gracefully (the same 'No results found.' empty state, no crash).</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Search term: @@@###$$$</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Type '@@@###$$$' into the category search box
 3. Verify the page does not error and shows 'No results found.'</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Typing special characters into the category search box must be handled gracefully (the same 'No results found.' empty state, no crash).</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr">
         <is>
           <t>Special-character input was handled gracefully with the expected empty-state message.</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J41" s="2" t="inlineStr">
         <is>
           <t>[PASS] Special-character search shows 'No results found.' without breaking the panel</t>
         </is>
       </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>LANDING_41</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>'World Tax Analyzer' tab keeps the user within WTA</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Clicking the already-active 'World Tax Analyzer' product tab must not navigate away from the WTA module.</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on the landing page (WTA already active).</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click the 'World Tax Analyzer' tab
 3. Verify the URL is still within /wta/</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Clicking the already-active 'World Tax Analyzer' product tab must not navigate away from the WTA module.</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>Clicking the already-active 'World Tax Analyzer' tab correctly kept the user within WTA, at https://regplus.kaz.com.bd/wta/Information.</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>[PASS] URL remains within /wta/ after clicking the already-active tab</t>
         </is>
       </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>LANDING_42</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>'Information' nav link points to /wta/Information</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>The 'Information' nav link's href must point to /wta/Information, consistent with it being the post-login landing page.</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Verify the 'Information' nav link's href</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>The 'Information' nav link's href must point to /wta/Information, consistent with it being the post-login landing page.</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr">
         <is>
           <t>'Information' nav link correctly points to /wta/Information.</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J43" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Information' nav link href contains /wta/Information</t>
         </is>
       </c>
-      <c r="K37" s="3" t="inlineStr">
+      <c r="K43" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/Dashboard/Dashboard_Test_Cases.xlsx
+++ b/test_data/Dashboard/Dashboard_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -805,6 +805,2187 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the Forms nav link navigates to the Forms module</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Forms' in the top nav must navigate to /wta/Forms.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click 'Forms' in the top navigation
+3. Verify the URL is /wta/Forms</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Forms' in the top nav must navigate to /wta/Forms.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Forms' navigated to https://regplus.kaz.com.bd/wta/Forms.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] URL contains /wta/Forms</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the Regulations nav link navigates to the Regulations module</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Regulations' in the top nav must navigate to /wta/Regulations.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click 'Regulations' in the top navigation
+3. Verify the URL is /wta/Regulations</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Regulations' in the top nav must navigate to /wta/Regulations.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Regulations' navigated to https://regplus.kaz.com.bd/wta/Regulations.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] URL contains /wta/Regulations</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>'Pillar 2' nav button is visible and enabled</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>The 'Pillar 2' dropdown trigger in the top nav must be visible and enabled. Its dropdown contents are covered in depth by the WTA Pillar2 Menu module - this is a light presence check only, to avoid duplicating that coverage.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify the 'Pillar 2' nav button is visible and enabled</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>The 'Pillar 2' dropdown trigger in the top nav must be visible and enabled. Its dropdown contents are covered in depth by the WTA Pillar2 Menu module - this is a light presence check only, to avoid duplicating that coverage.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>The 'Pillar 2' nav button is visible and enabled.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Pillar 2' nav button is visible and enabled</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>'Asia Pacific' region tab is selected by default</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>On first load, the 'Asia Pacific' region tab must carry the active/selected styling and 'Americas' must not.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify 'Asia Pacific' is the active region tab</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>On first load, the 'Asia Pacific' region tab must carry the active/selected styling and 'Americas' must not.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>'Asia Pacific' is the default active region tab.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Asia Pacific' is active and 'Americas' is not, by default</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Switching to the Americas region tab swaps the country list</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Americas' must show Americas countries (e.g. Brazil) and hide Asia Pacific countries (e.g. Australia).</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page, Asia Pacific selected by default.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click the 'Americas' region tab
+3. Verify Brazil is shown and Australia is hidden</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Americas' must show Americas countries (e.g. Brazil) and hide Asia Pacific countries (e.g. Australia).</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Switching to Americas correctly swapped the country list.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Brazil (Americas) is visible and Australia (Asia Pacific) is not</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Switching to the Europe region tab swaps the country list</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Europe' must show Europe countries (e.g. France) and hide Asia Pacific countries (e.g. Australia).</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click the 'Europe' region tab
+3. Verify France is shown and Australia is hidden</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Europe' must show Europe countries (e.g. France) and hide Asia Pacific countries (e.g. Australia).</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Switching to Europe correctly swapped the country list.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] France (Europe) is visible and Australia (Asia Pacific) is not</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Switching to the MEA region tab swaps the country list</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'MEA' must show MEA countries (e.g. Egypt) and hide Asia Pacific countries (e.g. Australia).</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click the 'MEA' region tab
+3. Verify Egypt is shown and Australia is hidden</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'MEA' must show MEA countries (e.g. Egypt) and hide Asia Pacific countries (e.g. Australia).</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Switching to MEA correctly swapped the country list.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Egypt (MEA) is visible and Australia (Asia Pacific) is not</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Clicking a region tab activates it and deactivates the previous one</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>After clicking 'Americas', it must carry the active/selected styling and 'Asia Pacific' must no longer carry it.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page, Asia Pacific active by default.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click the 'Americas' region tab
+3. Verify Americas is now active and Asia Pacific is not</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>After clicking 'Americas', it must carry the active/selected styling and 'Asia Pacific' must no longer carry it.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Americas' correctly toggled the active region tab.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Americas' is now active and 'Asia Pacific' is not</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Searching countries filters the jurisdiction checklist</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Typing 'Austra' in the country search box must show Australia and hide non-matching countries (e.g. Bangladesh).</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page, Asia Pacific region active.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Search term: Austra</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Type 'Austra' into the country search box
+3. Verify Australia is shown and Bangladesh is hidden</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Typing 'Austra' in the country search box must show Australia and hide non-matching countries (e.g. Bangladesh).</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Searching 'Austra' correctly filtered the country list.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Australia is shown and Bangladesh is hidden after searching 'Austra'</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Country search is case-insensitive</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Typing a lowercase search term ('austra') must still match 'Australia'.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Search term: austra (lowercase)</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Type 'austra' (lowercase) into the country search box
+3. Verify Australia is still shown</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Typing a lowercase search term ('austra') must still match 'Australia'.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Country search is case-insensitive: 'austra' matched Australia.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Australia is shown for the lowercase search 'austra'</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_16</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Searching for a non-existent country shows a 'no results' message</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Typing a term that matches no country must show 'No countries found matching "&lt;term&gt;"'.</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Search term: zzzznotreal</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Type 'zzzznotreal' into the country search box
+3. Verify the 'No countries found matching...' message appears</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Typing a term that matches no country must show 'No countries found matching "&lt;term&gt;"'.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>The 'No countries found matching...' empty-state message correctly appeared.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'No countries found matching...' message is shown</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_17</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Clearing the country search box restores the full list</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>After filtering to 'Austra' and then clearing the search box, the full country list (including Bangladesh) must reappear.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Search 'Austra'
+3. Clear the search box
+4. Verify Bangladesh reappears</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>After filtering to 'Austra' and then clearing the search box, the full country list (including Bangladesh) must reappear.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Clearing the country search box correctly restored the full country list.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Bangladesh reappears after clearing the country search</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_18</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Searching categories filters the category tree</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Typing 'Liability' in the category search box must show 'Liability to Tax' and hide non-matching categories (e.g. 'Tax Compliance').</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Search term: Liability</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Type 'Liability' into the category search box
+3. Verify 'Liability to Tax' is shown and 'Tax Compliance' is hidden</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Typing 'Liability' in the category search box must show 'Liability to Tax' and hide non-matching categories (e.g. 'Tax Compliance').</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Searching 'Liability' correctly filtered the category tree.</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Liability to Tax' is shown and 'Tax Compliance' is hidden after searching 'Liability'</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_19</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Searching for a non-existent category shows 'No results found.'</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Typing a term that matches no category must show 'No results found.' - note this wording differs from the country search's empty state, which echoes the search term.</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Search term: zzznotreal</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Type 'zzznotreal' into the category search box
+3. Verify 'No results found.' appears</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Typing a term that matches no category must show 'No results found.' - note this wording differs from the country search's empty state, which echoes the search term.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>The 'No results found.' empty-state message correctly appeared for the category search.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'No results found.' message is shown</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_20</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Clearing the category search box restores the full tree</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>After filtering to 'Liability' and then clearing the search box, the full category tree (including 'Tax Compliance') must reappear.</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Search 'Liability'
+3. Clear the search box
+4. Verify 'Tax Compliance' reappears</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>After filtering to 'Liability' and then clearing the search box, the full category tree (including 'Tax Compliance') must reappear.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Clearing the category search box correctly restored the full category tree.</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Tax Compliance' reappears after clearing the category search</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_21</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>'Check All' (categories) is unchecked by default</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>On first load, the 'Check All' category checkbox must be unchecked.</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify the 'Check All' checkbox is unchecked</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>On first load, the 'Check All' category checkbox must be unchecked.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>'Check All' is unchecked by default, as expected.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Check All' checkbox is unchecked by default</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_22</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>'Check All' checks every top-level category</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Check All' must check every top-level category, e.g. 'Liability to Tax'.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page, 'Check All' unchecked.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click 'Check All'
+3. Verify 'Liability to Tax' becomes checked</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Check All' must check every top-level category, e.g. 'Liability to Tax'.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Check All' correctly cascaded to check every top-level category.</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Check All' and 'Liability to Tax' are both checked after clicking 'Check All'</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_23</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Unchecking 'Check All' unchecks every category again</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>After checking 'Check All', clicking it again must uncheck every category, e.g. 'Liability to Tax'.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click 'Check All' to check it
+3. Click 'Check All' again to uncheck it
+4. Verify 'Liability to Tax' is unchecked</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>After checking 'Check All', clicking it again must uncheck every category, e.g. 'Liability to Tax'.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Toggling 'Check All' off correctly unchecked every category.</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Check All' and 'Liability to Tax' are both unchecked after toggling 'Check All' off</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_24</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Depth control expands the visible category tree</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Clicking Depth level '4' must reveal substantially more nested category content than the default view (confirmed live: default/1 ~585 characters of panel text vs. depth 4 ~3519 characters).</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Depth level: 4</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Record the category panel's text length
+3. Click Depth '4'
+4. Verify the panel's text length increased substantially</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Clicking Depth level '4' must reveal substantially more nested category content than the default view (confirmed live: default/1 ~585 characters of panel text vs. depth 4 ~3519 characters).</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Selecting Depth '4' expanded the category panel from 585 to 3519 characters of visible content.</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Category panel text length roughly doubles or more after selecting Depth 4</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_25</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Selecting a second country keeps the first one checked</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Checking 'Australia' then 'Bangladesh' must leave both checked - the jurisdiction panel supports multi-select.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Countries: Australia, Bangladesh</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Check 'Australia'
+3. Check 'Bangladesh'
+4. Verify both remain checked</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Checking 'Australia' then 'Bangladesh' must leave both checked - the jurisdiction panel supports multi-select.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>The jurisdiction panel correctly supports multi-select: both Australia and Bangladesh remained checked.</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Both 'Australia' and 'Bangladesh' remain checked (multi-select)</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Deselecting a checked country unchecks it</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Checking then re-clicking 'Australia' must uncheck it.</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Check 'Australia'
+3. Click 'Australia' again to uncheck it
+4. Verify it is unchecked</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Checking then re-clicking 'Australia' must uncheck it.</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Australia' a second time correctly unchecked it.</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Australia' is unchecked after clicking it a second time</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_27</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>'Workspace' product tab navigates to the Companydata dashboard</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the 'Workspace' tab must navigate to /companydata/dashboard/ - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click the 'Workspace' tab
+3. Verify the URL is /companydata/dashboard/</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the 'Workspace' tab must navigate to /companydata/dashboard/ - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Workspace' navigated to https://regplus.kaz.com.bd/companydata/dashboard/, the Companydata dashboard.</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] URL contains /companydata/dashboard/</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_28</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>'Transfer Pricing Analyzer' tab navigates to the TPA module</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the 'Transfer Pricing Analyzer' tab must navigate to /tpa/Home - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click the 'Transfer Pricing Analyzer' tab
+3. Verify the URL is /tpa/Home</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the 'Transfer Pricing Analyzer' tab must navigate to /tpa/Home - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Transfer Pricing Analyzer' navigated to https://regplus.kaz.com.bd/tpa/Home.</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] URL contains /tpa/Home</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_29</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>'RegBriefings' tab navigates to the RegBriefings module</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the 'RegBriefings' tab must navigate to /regbrief/home/ - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click the 'RegBriefings' tab
+3. Verify the URL contains /regbrief/home/</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the 'RegBriefings' tab must navigate to /regbrief/home/ - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'RegBriefings' navigated to https://regplus.kaz.com.bd/regbrief/home/myBriefings.</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] URL contains /regbrief/home/</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_30</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Browser back navigation returns from News to Information</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>After navigating to News via the top nav, using the browser's back button must return to /wta/Information.</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click 'News'
+3. Go back
+4. Verify the URL is /wta/Information</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>After navigating to News via the top nav, using the browser's back button must return to /wta/Information.</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Browser back correctly returned to https://regplus.kaz.com.bd/wta/Information.</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Browser back returns to /wta/Information</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_31</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Reloading the page preserves the authenticated session</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Reloading /wta/Information (F5) must keep the user authenticated and on the same page, not bounce them to the login page.</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Reload the page
+3. Verify the user is still on /wta/Information, not redirected to /auth/login</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Reloading /wta/Information (F5) must keep the user authenticated and on the same page, not bounce them to the login page.</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Reloading the page correctly preserved the authenticated session; still on https://regplus.kaz.com.bd/wta/Information.</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] User remains on /wta/Information after reload (not redirected to login)</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_32</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>The content placeholder is shown before any selection</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Before selecting a jurisdiction or category, the right panel must show 'Select Jurisdictions and Categories'.</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page, nothing selected.</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify the 'Select Jurisdictions and Categories' placeholder is visible</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Before selecting a jurisdiction or category, the right panel must show 'Select Jurisdictions and Categories'.</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>The 'Select Jurisdictions and Categories' placeholder is correctly shown before any selection.</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Placeholder text is visible before any selection</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_33</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Exactly 4 region tabs are present</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>The jurisdiction panel must show exactly 4 region tabs: Asia Pacific, Americas, Europe, MEA - no more, no fewer.</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify exactly 4 region tabs are present</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>The jurisdiction panel must show exactly 4 region tabs: Asia Pacific, Americas, Europe, MEA - no more, no fewer.</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Exactly the 4 expected region tabs (Asia Pacific, Americas, Europe, MEA) are present.</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Each of the 4 region tabs appears exactly once</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_34</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Asia Pacific region shows the expected number of countries</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>The Asia Pacific region (default) must list 25 countries, confirmed live (Australia through Vietnam).</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page, Asia Pacific active.</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Count the visible country checkboxes in the Asia Pacific list
+3. Verify the count is 25</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>The Asia Pacific region (default) must list 25 countries, confirmed live (Australia through Vietnam).</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Asia Pacific correctly lists 25 countries.</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Asia Pacific lists exactly 25 countries</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_35</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Exactly the 5 expected main nav items are present</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>The top nav must show Information, Pillar 2, News, Forms and Regulations - no more, no fewer.</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify each of the 5 main nav items appears exactly once</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>The top nav must show Information, Pillar 2, News, Forms and Regulations - no more, no fewer.</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Exactly the 5 expected main nav items are present.</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Each of the 5 main nav items appears exactly once</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_36</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Expected top-level categories are present in the tree</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>The category tree's default view must include the top-level categories 'Liability to Tax' and 'Tax Compliance'.</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify 'Liability to Tax' and 'Tax Compliance' are visible</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>The category tree's default view must include the top-level categories 'Liability to Tax' and 'Tax Compliance'.</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Both expected top-level categories are visible in the default tree view.</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Liability to Tax' and 'Tax Compliance' are both visible</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_37</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Exactly 4 product tabs are present</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>The product-tab row must show Workspace, World Tax Analyzer, Transfer Pricing Analyzer and RegBriefings - no more, no fewer.</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify each of the 4 product tabs appears exactly once</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>The product-tab row must show Workspace, World Tax Analyzer, Transfer Pricing Analyzer and RegBriefings - no more, no fewer.</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Exactly the 4 expected product tabs are present.</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Each of the 4 product tabs appears exactly once</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_38</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>A single category can be checked without using 'Check All'</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Liability to Tax's checkbox directly must check it, while 'Check All' remains unchecked (it only reflects when every category is checked). Note: the category LABEL text has no 'for' attribute linking it to its checkbox (confirmed live) - clicking the label is a no-op; only the checkbox input itself (or 'Check All', which has its own working handler) toggles selection.</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Category: Liability to Tax</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click 'Liability to Tax's checkbox
+3. Verify it is checked and 'Check All' remains unchecked</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Liability to Tax's checkbox directly must check it, while 'Check All' remains unchecked (it only reflects when every category is checked). Note: the category LABEL text has no 'for' attribute linking it to its checkbox (confirmed live) - clicking the label is a no-op; only the checkbox input itself (or 'Check All', which has its own working handler) toggles selection.</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>A single category can be selected independently of 'Check All'.</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Liability to Tax' is checked while 'Check All' remains unchecked</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_39</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Special-character input in the country search doesn't error</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Typing special characters into the country search box must be handled gracefully (the same 'No countries found...' empty state, no crash).</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Search term: @@@###$$$</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Type '@@@###$$$' into the country search box
+3. Verify the page does not error and shows the no-match message</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Typing special characters into the country search box must be handled gracefully (the same 'No countries found...' empty state, no crash).</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Special-character input was handled gracefully with the expected empty-state message.</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Special-character search shows the no-match message without breaking the panel</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_40</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Special-character input in the category search doesn't error</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Typing special characters into the category search box must be handled gracefully (the same 'No results found.' empty state, no crash).</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Search term: @@@###$$$</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Type '@@@###$$$' into the category search box
+3. Verify the page does not error and shows 'No results found.'</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Typing special characters into the category search box must be handled gracefully (the same 'No results found.' empty state, no crash).</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Special-character input was handled gracefully with the expected empty-state message.</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Special-character search shows 'No results found.' without breaking the panel</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_41</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>'World Tax Analyzer' tab keeps the user within WTA</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the already-active 'World Tax Analyzer' product tab must not navigate away from the WTA module.</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page (WTA already active).</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click the 'World Tax Analyzer' tab
+3. Verify the URL is still within /wta/</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the already-active 'World Tax Analyzer' product tab must not navigate away from the WTA module.</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the already-active 'World Tax Analyzer' tab correctly kept the user within WTA, at https://regplus.kaz.com.bd/wta/Information.</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] URL remains within /wta/ after clicking the already-active tab</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_42</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>'Information' nav link points to /wta/Information</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>The 'Information' nav link's href must point to /wta/Information, consistent with it being the post-login landing page.</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify the 'Information' nav link's href</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>The 'Information' nav link's href must point to /wta/Information, consistent with it being the post-login landing page.</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>'Information' nav link correctly points to /wta/Information.</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Information' nav link href contains /wta/Information</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/test_data/Dashboard/Dashboard_Test_Cases.xlsx
+++ b/test_data/Dashboard/Dashboard_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -537,7 +537,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Email: demo@reganalytics.com / Password: &lt;masked&gt;</t>
+          <t>Email: nasimsaker@gmail.com / Password: &lt;masked&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>After login the app landed on https://regplus.kaz.com.bd/wta/Information with the 'Jurisdictions and Categories' panel visible.</t>
+          <t>After login the app landed on https://regplusrc.reganalytics.com/wta/Information with the 'Jurisdictions and Categories' panel visible.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'News' navigated to https://regplus.kaz.com.bd/wta/News.</t>
+          <t>Clicking 'News' navigated to https://regplusrc.reganalytics.com/wta/News.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Forms' navigated to https://regplus.kaz.com.bd/wta/Forms.</t>
+          <t>Clicking 'Forms' navigated to https://regplusrc.reganalytics.com/wta/Forms.</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Regulations' navigated to https://regplus.kaz.com.bd/wta/Regulations.</t>
+          <t>Clicking 'Regulations' navigated to https://regplusrc.reganalytics.com/wta/Regulations.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Selecting Depth '4' expanded the category panel from 585 to 3519 characters of visible content.</t>
+          <t>Selecting Depth '4' expanded the category panel from 554 to 3114 characters of visible content.</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Workspace' navigated to https://regplus.kaz.com.bd/companydata/dashboard/, the Companydata dashboard.</t>
+          <t>Clicking 'Workspace' navigated to https://regplusrc.reganalytics.com/companydata/dashboard/, the Companydata dashboard.</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Transfer Pricing Analyzer' navigated to https://regplus.kaz.com.bd/tpa/Home.</t>
+          <t>Clicking 'Transfer Pricing Analyzer' navigated to https://regplusrc.reganalytics.com/tpa/Home.</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'RegBriefings' navigated to https://regplus.kaz.com.bd/regbrief/home/myBriefings.</t>
+          <t>Clicking 'RegBriefings' navigated to https://regplusrc.reganalytics.com/regbrief/home/myBriefings.</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Browser back correctly returned to https://regplus.kaz.com.bd/wta/Information.</t>
+          <t>Browser back correctly returned to https://regplusrc.reganalytics.com/wta/Information.</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Reloading the page correctly preserved the authenticated session; still on https://regplus.kaz.com.bd/wta/Information.</t>
+          <t>Reloading the page correctly preserved the authenticated session; still on https://regplusrc.reganalytics.com/wta/Information.</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2462,7 +2462,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>LANDING_34</t>
+          <t>LANDING_35</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2472,17 +2472,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Asia Pacific region shows the expected number of countries</t>
+          <t>Exactly the 5 expected main nav items are present</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>The Asia Pacific region (default) must list 25 countries, confirmed live (Australia through Vietnam).</t>
+          <t>The top nav must show Information, Pillar 2, News, Forms and Regulations - no more, no fewer.</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on the landing page, Asia Pacific active.</t>
+          <t>User is logged in and on the landing page.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2493,23 +2493,22 @@
       <c r="G35" s="2" t="inlineStr">
         <is>
           <t>1. Log in
-2. Count the visible country checkboxes in the Asia Pacific list
-3. Verify the count is 25</t>
+2. Verify each of the 5 main nav items appears exactly once</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>The Asia Pacific region (default) must list 25 countries, confirmed live (Australia through Vietnam).</t>
+          <t>The top nav must show Information, Pillar 2, News, Forms and Regulations - no more, no fewer.</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Asia Pacific correctly lists 25 countries.</t>
+          <t>Exactly the 5 expected main nav items are present.</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Asia Pacific lists exactly 25 countries</t>
+          <t>[PASS] Each of the 5 main nav items appears exactly once</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
@@ -2521,7 +2520,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>LANDING_35</t>
+          <t>LANDING_36</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2531,12 +2530,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Exactly the 5 expected main nav items are present</t>
+          <t>Expected top-level categories are present in the tree</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>The top nav must show Information, Pillar 2, News, Forms and Regulations - no more, no fewer.</t>
+          <t>The category tree's default view must include the top-level categories 'Liability to Tax' and 'Tax Compliance'.</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2552,22 +2551,22 @@
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1. Log in
-2. Verify each of the 5 main nav items appears exactly once</t>
+2. Verify 'Liability to Tax' and 'Tax Compliance' are visible</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>The top nav must show Information, Pillar 2, News, Forms and Regulations - no more, no fewer.</t>
+          <t>The category tree's default view must include the top-level categories 'Liability to Tax' and 'Tax Compliance'.</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Exactly the 5 expected main nav items are present.</t>
+          <t>Both expected top-level categories are visible in the default tree view.</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Each of the 5 main nav items appears exactly once</t>
+          <t>[PASS] 'Liability to Tax' and 'Tax Compliance' are both visible</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
@@ -2579,7 +2578,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>LANDING_36</t>
+          <t>LANDING_37</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2589,12 +2588,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Expected top-level categories are present in the tree</t>
+          <t>Exactly 4 product tabs are present</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>The category tree's default view must include the top-level categories 'Liability to Tax' and 'Tax Compliance'.</t>
+          <t>The product-tab row must show Workspace, World Tax Analyzer, Transfer Pricing Analyzer and RegBriefings - no more, no fewer.</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2610,22 +2609,22 @@
       <c r="G37" s="2" t="inlineStr">
         <is>
           <t>1. Log in
-2. Verify 'Liability to Tax' and 'Tax Compliance' are visible</t>
+2. Verify each of the 4 product tabs appears exactly once</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>The category tree's default view must include the top-level categories 'Liability to Tax' and 'Tax Compliance'.</t>
+          <t>The product-tab row must show Workspace, World Tax Analyzer, Transfer Pricing Analyzer and RegBriefings - no more, no fewer.</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Both expected top-level categories are visible in the default tree view.</t>
+          <t>Exactly the 4 expected product tabs are present.</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>[PASS] 'Liability to Tax' and 'Tax Compliance' are both visible</t>
+          <t>[PASS] Each of the 4 product tabs appears exactly once</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
@@ -2637,7 +2636,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>LANDING_37</t>
+          <t>LANDING_38</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2647,12 +2646,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Exactly 4 product tabs are present</t>
+          <t>A single category can be checked without using 'Check All'</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>The product-tab row must show Workspace, World Tax Analyzer, Transfer Pricing Analyzer and RegBriefings - no more, no fewer.</t>
+          <t>Clicking 'Liability to Tax's checkbox directly must check it, while 'Check All' remains unchecked (it only reflects when every category is checked). Note: the category LABEL text has no 'for' attribute linking it to its checkbox (confirmed live) - clicking the label is a no-op; only the checkbox input itself (or 'Check All', which has its own working handler) toggles selection.</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2662,28 +2661,29 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Category: Liability to Tax</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
           <t>1. Log in
-2. Verify each of the 4 product tabs appears exactly once</t>
+2. Click 'Liability to Tax's checkbox
+3. Verify it is checked and 'Check All' remains unchecked</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>The product-tab row must show Workspace, World Tax Analyzer, Transfer Pricing Analyzer and RegBriefings - no more, no fewer.</t>
+          <t>Clicking 'Liability to Tax's checkbox directly must check it, while 'Check All' remains unchecked (it only reflects when every category is checked). Note: the category LABEL text has no 'for' attribute linking it to its checkbox (confirmed live) - clicking the label is a no-op; only the checkbox input itself (or 'Check All', which has its own working handler) toggles selection.</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Exactly the 4 expected product tabs are present.</t>
+          <t>A single category can be selected independently of 'Check All'.</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Each of the 4 product tabs appears exactly once</t>
+          <t>[PASS] 'Liability to Tax' is checked while 'Check All' remains unchecked</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
@@ -2695,7 +2695,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>LANDING_38</t>
+          <t>LANDING_39</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>A single category can be checked without using 'Check All'</t>
+          <t>Special-character input in the country search doesn't error</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Liability to Tax's checkbox directly must check it, while 'Check All' remains unchecked (it only reflects when every category is checked). Note: the category LABEL text has no 'for' attribute linking it to its checkbox (confirmed live) - clicking the label is a no-op; only the checkbox input itself (or 'Check All', which has its own working handler) toggles selection.</t>
+          <t>Typing special characters into the country search box must be handled gracefully (the same 'No countries found...' empty state, no crash).</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2720,29 +2720,29 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Category: Liability to Tax</t>
+          <t>Search term: @@@###$$$</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
           <t>1. Log in
-2. Click 'Liability to Tax's checkbox
-3. Verify it is checked and 'Check All' remains unchecked</t>
+2. Type '@@@###$$$' into the country search box
+3. Verify the page does not error and shows the no-match message</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Liability to Tax's checkbox directly must check it, while 'Check All' remains unchecked (it only reflects when every category is checked). Note: the category LABEL text has no 'for' attribute linking it to its checkbox (confirmed live) - clicking the label is a no-op; only the checkbox input itself (or 'Check All', which has its own working handler) toggles selection.</t>
+          <t>Typing special characters into the country search box must be handled gracefully (the same 'No countries found...' empty state, no crash).</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>A single category can be selected independently of 'Check All'.</t>
+          <t>Special-character input was handled gracefully with the expected empty-state message.</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>[PASS] 'Liability to Tax' is checked while 'Check All' remains unchecked</t>
+          <t>[PASS] Special-character search shows the no-match message without breaking the panel</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
@@ -2754,7 +2754,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>LANDING_39</t>
+          <t>LANDING_40</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Special-character input in the country search doesn't error</t>
+          <t>Special-character input in the category search doesn't error</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Typing special characters into the country search box must be handled gracefully (the same 'No countries found...' empty state, no crash).</t>
+          <t>Typing special characters into the category search box must be handled gracefully (the same 'No results found.' empty state, no crash).</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2785,13 +2785,13 @@
       <c r="G40" s="2" t="inlineStr">
         <is>
           <t>1. Log in
-2. Type '@@@###$$$' into the country search box
-3. Verify the page does not error and shows the no-match message</t>
+2. Type '@@@###$$$' into the category search box
+3. Verify the page does not error and shows 'No results found.'</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Typing special characters into the country search box must be handled gracefully (the same 'No countries found...' empty state, no crash).</t>
+          <t>Typing special characters into the category search box must be handled gracefully (the same 'No results found.' empty state, no crash).</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Special-character search shows the no-match message without breaking the panel</t>
+          <t>[PASS] Special-character search shows 'No results found.' without breaking the panel</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
@@ -2813,7 +2813,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>LANDING_40</t>
+          <t>LANDING_41</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2823,44 +2823,44 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Special-character input in the category search doesn't error</t>
+          <t>'World Tax Analyzer' tab keeps the user within WTA</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Typing special characters into the category search box must be handled gracefully (the same 'No results found.' empty state, no crash).</t>
+          <t>Clicking the already-active 'World Tax Analyzer' product tab must not navigate away from the WTA module.</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on the landing page.</t>
+          <t>User is logged in and on the landing page (WTA already active).</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Search term: @@@###$$$</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
           <t>1. Log in
-2. Type '@@@###$$$' into the category search box
-3. Verify the page does not error and shows 'No results found.'</t>
+2. Click the 'World Tax Analyzer' tab
+3. Verify the URL is still within /wta/</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Typing special characters into the category search box must be handled gracefully (the same 'No results found.' empty state, no crash).</t>
+          <t>Clicking the already-active 'World Tax Analyzer' product tab must not navigate away from the WTA module.</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Special-character input was handled gracefully with the expected empty-state message.</t>
+          <t>Clicking the already-active 'World Tax Analyzer' tab correctly kept the user within WTA, at https://regplusrc.reganalytics.com/wta/Information.</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Special-character search shows 'No results found.' without breaking the panel</t>
+          <t>[PASS] URL remains within /wta/ after clicking the already-active tab</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
@@ -2872,7 +2872,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>LANDING_41</t>
+          <t>LANDING_42</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2882,17 +2882,17 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>'World Tax Analyzer' tab keeps the user within WTA</t>
+          <t>'Information' nav link points to /wta/Information</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Clicking the already-active 'World Tax Analyzer' product tab must not navigate away from the WTA module.</t>
+          <t>The 'Information' nav link's href must point to /wta/Information, consistent with it being the post-login landing page.</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on the landing page (WTA already active).</t>
+          <t>User is logged in and on the landing page.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2903,84 +2903,25 @@
       <c r="G42" s="2" t="inlineStr">
         <is>
           <t>1. Log in
-2. Click the 'World Tax Analyzer' tab
-3. Verify the URL is still within /wta/</t>
+2. Verify the 'Information' nav link's href</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Clicking the already-active 'World Tax Analyzer' product tab must not navigate away from the WTA module.</t>
+          <t>The 'Information' nav link's href must point to /wta/Information, consistent with it being the post-login landing page.</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Clicking the already-active 'World Tax Analyzer' tab correctly kept the user within WTA, at https://regplus.kaz.com.bd/wta/Information.</t>
+          <t>'Information' nav link correctly points to /wta/Information.</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>[PASS] URL remains within /wta/ after clicking the already-active tab</t>
+          <t>[PASS] 'Information' nav link href contains /wta/Information</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>LANDING_42</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>'Information' nav link points to /wta/Information</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>The 'Information' nav link's href must point to /wta/Information, consistent with it being the post-login landing page.</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Verify the 'Information' nav link's href</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>The 'Information' nav link's href must point to /wta/Information, consistent with it being the post-login landing page.</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>'Information' nav link correctly points to /wta/Information.</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'Information' nav link href contains /wta/Information</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/Dashboard/Dashboard_Test_Cases.xlsx
+++ b/test_data/Dashboard/Dashboard_Test_Cases.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -620,25 +620,25 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Missing nav links: ['Information', 'News']. Missing tabs: [].</t>
+          <t>All main navigation links (Information, News, Forms, Regulations) and product tabs (Workspace, World Tax Analyzer, Transfer Pricing Analyzer, RegBriefings) are visible.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>[FAIL] Information/News/Forms/Regulations links are visible
+          <t>[PASS] Information/News/Forms/Regulations links are visible
 [PASS] Workspace/World Tax Analyzer/Transfer Pricing Analyzer/RegBriefings tabs are visible</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>LANDING_08</t>
+          <t>LANDING_03</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>'Pillar 2' nav button is visible and enabled</t>
+          <t>Clicking the News nav link navigates to the News module</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>The 'Pillar 2' dropdown trigger in the top nav must be visible and enabled. Its dropdown contents are covered in depth by the WTA Pillar2 Menu module - this is a light presence check only, to avoid duplicating that coverage.</t>
+          <t>Clicking 'News' in the top nav must navigate to /wta/News.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -669,22 +669,23 @@
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1. Log in
-2. Verify the 'Pillar 2' nav button is visible and enabled</t>
+2. Click 'News' in the top navigation
+3. Verify the URL is /wta/News</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>The 'Pillar 2' dropdown trigger in the top nav must be visible and enabled. Its dropdown contents are covered in depth by the WTA Pillar2 Menu module - this is a light presence check only, to avoid duplicating that coverage.</t>
+          <t>Clicking 'News' in the top nav must navigate to /wta/News.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>The 'Pillar 2' nav button is visible and enabled.</t>
+          <t>Clicking 'News' navigated to https://regplus.reganalytics.com/wta/News.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>[PASS] 'Pillar 2' nav button is visible and enabled</t>
+          <t>[PASS] URL contains /wta/News</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -696,7 +697,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>LANDING_09</t>
+          <t>LANDING_04</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -706,17 +707,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>'Asia Pacific' region tab is selected by default</t>
+          <t>The cookie consent banner can be dismissed</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>On first load, the 'Asia Pacific' region tab must carry the active/selected styling and 'Americas' must not.</t>
+          <t>The 'Please review our Terms and Conditions...' banner must disappear after clicking Accept.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on the landing page.</t>
+          <t>User is logged in; the cookie banner is showing (first session load).</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -727,22 +728,24 @@
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. Log in
-2. Verify 'Asia Pacific' is the active region tab</t>
+2. Verify the cookie banner is visible
+3. Click Accept
+4. Verify the banner is no longer visible</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>On first load, the 'Asia Pacific' region tab must carry the active/selected styling and 'Americas' must not.</t>
+          <t>The 'Please review our Terms and Conditions...' banner must disappear after clicking Accept.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>'Asia Pacific' is the default active region tab.</t>
+          <t>Clicking Accept dismissed the cookie banner.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>[PASS] 'Asia Pacific' is active and 'Americas' is not, by default</t>
+          <t>[PASS] Cookie banner is no longer visible after Accept</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -754,7 +757,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>LANDING_21</t>
+          <t>LANDING_05</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -764,104 +767,1519 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>'Check All' (categories) is unchecked by default</t>
+          <t>Selecting a jurisdiction checks its checkbox</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>On first load, the 'Check All' category checkbox must be unchecked.</t>
+          <t>Clicking a country in the Jurisdictions panel (e.g. Australia) must check its checkbox, confirming the left panel is interactive.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on the landing page.</t>
+          <t>User is logged in and on the landing page, Asia Pacific region selected by default.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Country: Australia</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1. Log in
-2. Verify the 'Check All' checkbox is unchecked</t>
+2. Click the 'Australia' checkbox in the Jurisdictions panel
+3. Verify the checkbox becomes checked</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>On first load, the 'Check All' category checkbox must be unchecked.</t>
+          <t>Clicking a country in the Jurisdictions panel (e.g. Australia) must check its checkbox, confirming the left panel is interactive.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>'Check All' was not unchecked by default (state: None).</t>
+          <t>Clicking 'Australia' in the Jurisdictions panel checked its checkbox, confirming the panel responds to selection.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>[FAIL] 'Check All' checkbox is unchecked by default</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>[PASS] Australia's checkbox is checked after clicking it</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>LANDING_07</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the Regulations nav link navigates to the Regulations module</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Regulations' in the top nav must navigate to /wta/Regulations.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click 'Regulations' in the top navigation
+3. Verify the URL is /wta/Regulations</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Regulations' in the top nav must navigate to /wta/Regulations.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Regulations' navigated to https://regplus.reganalytics.com/wta/Regulations.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] URL contains /wta/Regulations</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_08</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>'Pillar 2' nav button is visible and enabled</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>The 'Pillar 2' dropdown trigger in the top nav must be visible and enabled. Its dropdown contents are covered in depth by the WTA Pillar2 Menu module - this is a light presence check only, to avoid duplicating that coverage.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify the 'Pillar 2' nav button is visible and enabled</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>The 'Pillar 2' dropdown trigger in the top nav must be visible and enabled. Its dropdown contents are covered in depth by the WTA Pillar2 Menu module - this is a light presence check only, to avoid duplicating that coverage.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>The 'Pillar 2' nav button is visible and enabled.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Pillar 2' nav button is visible and enabled</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_10</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Switching to the Americas region tab swaps the country list</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Americas' must show Americas countries (e.g. Brazil) and hide Asia Pacific countries (e.g. Australia).</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page, Asia Pacific selected by default.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click the 'Americas' region tab
+3. Verify Brazil is shown and Australia is hidden</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Americas' must show Americas countries (e.g. Brazil) and hide Asia Pacific countries (e.g. Australia).</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Switching to Americas correctly swapped the country list.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Brazil (Americas) is visible and Australia (Asia Pacific) is not</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_11</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Switching to the Europe region tab swaps the country list</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Europe' must show Europe countries (e.g. France) and hide Asia Pacific countries (e.g. Australia).</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click the 'Europe' region tab
+3. Verify France is shown and Australia is hidden</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Europe' must show Europe countries (e.g. France) and hide Asia Pacific countries (e.g. Australia).</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Switching to Europe correctly swapped the country list.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] France (Europe) is visible and Australia (Asia Pacific) is not</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_13</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Clicking a region tab activates it and deactivates the previous one</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>After clicking 'Americas', it must carry the active/selected styling and 'Asia Pacific' must no longer carry it.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page, Asia Pacific active by default.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click the 'Americas' region tab
+3. Verify Americas is now active and Asia Pacific is not</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>After clicking 'Americas', it must carry the active/selected styling and 'Asia Pacific' must no longer carry it.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Americas' correctly toggled the active region tab.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Americas' is now active and 'Asia Pacific' is not</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_15</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Country search is case-insensitive</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Typing a lowercase search term ('austra') must still match 'Australia'.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Search term: austra (lowercase)</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Type 'austra' (lowercase) into the country search box
+3. Verify Australia is still shown</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Typing a lowercase search term ('austra') must still match 'Australia'.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Country search is case-insensitive: 'austra' matched Australia.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Australia is shown for the lowercase search 'austra'</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_16</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Searching for a non-existent country shows a 'no results' message</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Typing a term that matches no country must show 'No countries found matching "&lt;term&gt;"'.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Search term: zzzznotreal</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Type 'zzzznotreal' into the country search box
+3. Verify the 'No countries found matching...' message appears</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Typing a term that matches no country must show 'No countries found matching "&lt;term&gt;"'.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>The 'No countries found matching...' empty-state message correctly appeared.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'No countries found matching...' message is shown</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_18</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Searching categories filters the category tree</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Typing 'Liability' in the category search box must show 'Liability to Tax' and hide non-matching categories (e.g. 'Tax Compliance').</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Search term: Liability</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Type 'Liability' into the category search box
+3. Verify 'Liability to Tax' is shown and 'Tax Compliance' is hidden</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Typing 'Liability' in the category search box must show 'Liability to Tax' and hide non-matching categories (e.g. 'Tax Compliance').</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Searching 'Liability' correctly filtered the category tree.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Liability to Tax' is shown and 'Tax Compliance' is hidden after searching 'Liability'</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_19</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Searching for a non-existent category shows 'No results found.'</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Typing a term that matches no category must show 'No results found.' - note this wording differs from the country search's empty state, which echoes the search term.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Search term: zzznotreal</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Type 'zzznotreal' into the category search box
+3. Verify 'No results found.' appears</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Typing a term that matches no category must show 'No results found.' - note this wording differs from the country search's empty state, which echoes the search term.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>The 'No results found.' empty-state message correctly appeared for the category search.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'No results found.' message is shown</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_20</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Clearing the category search box restores the full tree</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>After filtering to 'Liability' and then clearing the search box, the full category tree (including 'Tax Compliance') must reappear.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Search 'Liability'
+3. Clear the search box
+4. Verify 'Tax Compliance' reappears</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>After filtering to 'Liability' and then clearing the search box, the full category tree (including 'Tax Compliance') must reappear.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Clearing the category search box correctly restored the full category tree.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Tax Compliance' reappears after clearing the category search</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_21</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>'Check All' (categories) is unchecked by default</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>On first load, the 'Check All' category checkbox must be unchecked.</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify the 'Check All' checkbox is unchecked</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>On first load, the 'Check All' category checkbox must be unchecked.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>'Check All' was not unchecked by default (state: None).</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>[FAIL] 'Check All' checkbox is unchecked by default</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_23</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Unchecking 'Check All' unchecks every category again</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>After checking 'Check All', clicking it again must uncheck every category, e.g. 'Liability to Tax'.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click 'Check All' to check it
+3. Click 'Check All' again to uncheck it
+4. Verify 'Liability to Tax' is unchecked</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>After checking 'Check All', clicking it again must uncheck every category, e.g. 'Liability to Tax'.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Toggling 'Check All' off correctly unchecked every category.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Check All' and 'Liability to Tax' are both unchecked after toggling 'Check All' off</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_25</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Selecting a second country keeps the first one checked</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Checking 'Australia' then 'Bangladesh' must leave both checked - the jurisdiction panel supports multi-select.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Countries: Australia, Bangladesh</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Check 'Australia'
+3. Check 'Bangladesh'
+4. Verify both remain checked</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Checking 'Australia' then 'Bangladesh' must leave both checked - the jurisdiction panel supports multi-select.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>The jurisdiction panel correctly supports multi-select: both Australia and Bangladesh remained checked.</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Both 'Australia' and 'Bangladesh' remain checked (multi-select)</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_27</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>'Workspace' product tab navigates to the Companydata dashboard</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the 'Workspace' tab must navigate to /companydata/dashboard/ - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click the 'Workspace' tab
+3. Verify the URL is /companydata/dashboard/</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the 'Workspace' tab must navigate to /companydata/dashboard/ - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Workspace' navigated to https://regplus.reganalytics.com/companydata/dashboard/, the Companydata dashboard.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] URL contains /companydata/dashboard/</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_28</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>'Transfer Pricing Analyzer' tab navigates to the TPA module</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the 'Transfer Pricing Analyzer' tab must navigate to /tpa/Home - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click the 'Transfer Pricing Analyzer' tab
+3. Verify the URL is /tpa/Home</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the 'Transfer Pricing Analyzer' tab must navigate to /tpa/Home - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Transfer Pricing Analyzer' navigated to https://regplus.reganalytics.com/tpa/Home.</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] URL contains /tpa/Home</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_30</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Browser back navigation returns from News to Information</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>After navigating to News via the top nav, using the browser's back button must return to /wta/Information.</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click 'News'
+3. Go back
+4. Verify the URL is /wta/Information</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>After navigating to News via the top nav, using the browser's back button must return to /wta/Information.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Browser back correctly returned to https://regplus.reganalytics.com/wta/Information.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Browser back returns to /wta/Information</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_31</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Reloading the page preserves the authenticated session</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Reloading /wta/Information (F5) must keep the user authenticated and on the same page, not bounce them to the login page.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Reload the page
+3. Verify the user is still on /wta/Information, not redirected to /auth/login</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Reloading /wta/Information (F5) must keep the user authenticated and on the same page, not bounce them to the login page.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Reloading the page correctly preserved the authenticated session; still on https://regplus.reganalytics.com/wta/Information.</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] User remains on /wta/Information after reload (not redirected to login)</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>LANDING_32</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>The content placeholder is shown before any selection</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Before selecting a jurisdiction or category, the right panel must show 'Select Jurisdictions and Categories'.</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on the landing page, nothing selected.</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Verify the 'Select Jurisdictions and Categories' placeholder is visible</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Before selecting a jurisdiction or category, the right panel must show 'Select Jurisdictions and Categories'.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>The 'Select Jurisdictions and Categories' placeholder is correctly shown before any selection.</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Placeholder text is visible before any selection</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>The expected placeholder text was not visible.</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>[FAIL] Placeholder text is visible before any selection</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_34</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Asia Pacific region shows the expected number of countries</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>The Asia Pacific region (default) must list 25 countries, confirmed live (Australia through Vietnam).</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page, Asia Pacific active.</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Count the visible country checkboxes in the Asia Pacific list
+3. Verify the count is 25</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>The Asia Pacific region (default) must list 25 countries, confirmed live (Australia through Vietnam).</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Asia Pacific correctly lists 25 countries.</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Asia Pacific lists exactly 25 countries</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_35</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Exactly the 5 expected main nav items are present</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>The top nav must show Information, Pillar 2, News, Forms and Regulations - no more, no fewer.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify each of the 5 main nav items appears exactly once</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>The top nav must show Information, Pillar 2, News, Forms and Regulations - no more, no fewer.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Exactly the 5 expected main nav items are present.</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Each of the 5 main nav items appears exactly once</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_36</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Expected top-level categories are present in the tree</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>The category tree's default view must include the top-level categories 'Liability to Tax' and 'Tax Compliance'.</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify 'Liability to Tax' and 'Tax Compliance' are visible</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>The category tree's default view must include the top-level categories 'Liability to Tax' and 'Tax Compliance'.</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Missing expected categories: Liability to Tax=False, Tax Compliance=False.</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>[FAIL] 'Liability to Tax' and 'Tax Compliance' are both visible</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_37</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Exactly 4 product tabs are present</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>The product-tab row must show Workspace, World Tax Analyzer, Transfer Pricing Analyzer and RegBriefings - no more, no fewer.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify each of the 4 product tabs appears exactly once</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>The product-tab row must show Workspace, World Tax Analyzer, Transfer Pricing Analyzer and RegBriefings - no more, no fewer.</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Exactly the 4 expected product tabs are present.</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Each of the 4 product tabs appears exactly once</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_38</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>A single category can be checked without using 'Check All'</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Liability to Tax's checkbox directly must check it, while 'Check All' remains unchecked (it only reflects when every category is checked). Note: the category LABEL text has no 'for' attribute linking it to its checkbox (confirmed live) - clicking the label is a no-op; only the checkbox input itself (or 'Check All', which has its own working handler) toggles selection.</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Category: Liability to Tax</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click 'Liability to Tax's checkbox
+3. Verify it is checked and 'Check All' remains unchecked</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Liability to Tax's checkbox directly must check it, while 'Check All' remains unchecked (it only reflects when every category is checked). Note: the category LABEL text has no 'for' attribute linking it to its checkbox (confirmed live) - clicking the label is a no-op; only the checkbox input itself (or 'Check All', which has its own working handler) toggles selection.</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>A single category can be selected independently of 'Check All'.</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Liability to Tax' is checked while 'Check All' remains unchecked</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_41</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>'World Tax Analyzer' tab keeps the user within WTA</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the already-active 'World Tax Analyzer' product tab must not navigate away from the WTA module.</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page (WTA already active).</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click the 'World Tax Analyzer' tab
+3. Verify the URL is still within /wta/</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the already-active 'World Tax Analyzer' product tab must not navigate away from the WTA module.</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the already-active 'World Tax Analyzer' tab correctly kept the user within WTA, at https://regplus.reganalytics.com/wta/Information.</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] URL remains within /wta/ after clicking the already-active tab</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_42</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>'Information' nav link points to /wta/Information</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>The 'Information' nav link's href must point to /wta/Information, consistent with it being the post-login landing page.</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify the 'Information' nav link's href</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>The 'Information' nav link's href must point to /wta/Information, consistent with it being the post-login landing page.</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>'Information' nav link correctly points to /wta/Information.</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Information' nav link href contains /wta/Information</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/Dashboard/Dashboard_Test_Cases.xlsx
+++ b/test_data/Dashboard/Dashboard_Test_Cases.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -47,11 +47,6 @@
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -65,7 +60,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -74,9 +69,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -444,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -545,7 +537,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Email: monir.smh@gmail.com / Password: &lt;masked&gt;</t>
+          <t>Email: demo@reganalytics.com / Password: &lt;masked&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -562,7 +554,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>After login the app landed on https://regplus.reganalytics.com/wta/Information with the 'Jurisdictions and Categories' panel visible.</t>
+          <t>After login the app landed on https://regplus.kaz.com.bd/wta/Information with the 'Jurisdictions and Categories' panel visible.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -680,7 +672,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'News' navigated to https://regplus.reganalytics.com/wta/News.</t>
+          <t>Clicking 'News' navigated to https://regplus.kaz.com.bd/wta/News.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -816,112 +808,113 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>LANDING_06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the Forms nav link navigates to the Forms module</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Forms' in the top nav must navigate to /wta/Forms.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click 'Forms' in the top navigation
+3. Verify the URL is /wta/Forms</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Forms' in the top nav must navigate to /wta/Forms.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Forms' navigated to https://regplus.kaz.com.bd/wta/Forms.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] URL contains /wta/Forms</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>LANDING_07</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Clicking the Regulations nav link navigates to the Regulations module</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Regulations' in the top nav must navigate to /wta/Regulations.</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click 'Regulations' in the top navigation
 3. Verify the URL is /wta/Regulations</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Regulations' in the top nav must navigate to /wta/Regulations.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Regulations' navigated to https://regplus.reganalytics.com/wta/Regulations.</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Regulations' navigated to https://regplus.kaz.com.bd/wta/Regulations.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>[PASS] URL contains /wta/Regulations</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>LANDING_08</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>'Pillar 2' nav button is visible and enabled</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>The 'Pillar 2' dropdown trigger in the top nav must be visible and enabled. Its dropdown contents are covered in depth by the WTA Pillar2 Menu module - this is a light presence check only, to avoid duplicating that coverage.</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Verify the 'Pillar 2' nav button is visible and enabled</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>The 'Pillar 2' dropdown trigger in the top nav must be visible and enabled. Its dropdown contents are covered in depth by the WTA Pillar2 Menu module - this is a light presence check only, to avoid duplicating that coverage.</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>The 'Pillar 2' nav button is visible and enabled.</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'Pillar 2' nav button is visible and enabled</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -933,448 +926,742 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>LANDING_08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>'Pillar 2' nav button is visible and enabled</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>The 'Pillar 2' dropdown trigger in the top nav must be visible and enabled. Its dropdown contents are covered in depth by the WTA Pillar2 Menu module - this is a light presence check only, to avoid duplicating that coverage.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify the 'Pillar 2' nav button is visible and enabled</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>The 'Pillar 2' dropdown trigger in the top nav must be visible and enabled. Its dropdown contents are covered in depth by the WTA Pillar2 Menu module - this is a light presence check only, to avoid duplicating that coverage.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>The 'Pillar 2' nav button is visible and enabled.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Pillar 2' nav button is visible and enabled</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>'Asia Pacific' region tab is selected by default</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>On first load, the 'Asia Pacific' region tab must carry the active/selected styling and 'Americas' must not.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify 'Asia Pacific' is the active region tab</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>On first load, the 'Asia Pacific' region tab must carry the active/selected styling and 'Americas' must not.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>'Asia Pacific' is the default active region tab.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Asia Pacific' is active and 'Americas' is not, by default</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>LANDING_10</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Switching to the Americas region tab swaps the country list</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Americas' must show Americas countries (e.g. Brazil) and hide Asia Pacific countries (e.g. Australia).</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on the landing page, Asia Pacific selected by default.</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click the 'Americas' region tab
 3. Verify Brazil is shown and Australia is hidden</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Americas' must show Americas countries (e.g. Brazil) and hide Asia Pacific countries (e.g. Australia).</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Switching to Americas correctly swapped the country list.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>[PASS] Brazil (Americas) is visible and Australia (Asia Pacific) is not</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>LANDING_11</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Switching to the Europe region tab swaps the country list</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Europe' must show Europe countries (e.g. France) and hide Asia Pacific countries (e.g. Australia).</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click the 'Europe' region tab
 3. Verify France is shown and Australia is hidden</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Europe' must show Europe countries (e.g. France) and hide Asia Pacific countries (e.g. Australia).</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Switching to Europe correctly swapped the country list.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>[PASS] France (Europe) is visible and Australia (Asia Pacific) is not</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Switching to the MEA region tab swaps the country list</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'MEA' must show MEA countries (e.g. Egypt) and hide Asia Pacific countries (e.g. Australia).</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click the 'MEA' region tab
+3. Verify Egypt is shown and Australia is hidden</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'MEA' must show MEA countries (e.g. Egypt) and hide Asia Pacific countries (e.g. Australia).</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Switching to MEA correctly swapped the country list.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Egypt (MEA) is visible and Australia (Asia Pacific) is not</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>LANDING_13</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Clicking a region tab activates it and deactivates the previous one</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>After clicking 'Americas', it must carry the active/selected styling and 'Asia Pacific' must no longer carry it.</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on the landing page, Asia Pacific active by default.</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click the 'Americas' region tab
 3. Verify Americas is now active and Asia Pacific is not</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>After clicking 'Americas', it must carry the active/selected styling and 'Asia Pacific' must no longer carry it.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Americas' correctly toggled the active region tab.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Americas' is now active and 'Asia Pacific' is not</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Searching countries filters the jurisdiction checklist</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Typing 'Austra' in the country search box must show Australia and hide non-matching countries (e.g. Bangladesh).</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page, Asia Pacific region active.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Search term: Austra</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Type 'Austra' into the country search box
+3. Verify Australia is shown and Bangladesh is hidden</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Typing 'Austra' in the country search box must show Australia and hide non-matching countries (e.g. Bangladesh).</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Searching 'Austra' correctly filtered the country list.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Australia is shown and Bangladesh is hidden after searching 'Austra'</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>LANDING_15</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Country search is case-insensitive</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Typing a lowercase search term ('austra') must still match 'Australia'.</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Search term: austra (lowercase)</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Type 'austra' (lowercase) into the country search box
 3. Verify Australia is still shown</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Typing a lowercase search term ('austra') must still match 'Australia'.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>Country search is case-insensitive: 'austra' matched Australia.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>[PASS] Australia is shown for the lowercase search 'austra'</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>LANDING_16</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Searching for a non-existent country shows a 'no results' message</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Typing a term that matches no country must show 'No countries found matching "&lt;term&gt;"'.</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Search term: zzzznotreal</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Type 'zzzznotreal' into the country search box
 3. Verify the 'No countries found matching...' message appears</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Typing a term that matches no country must show 'No countries found matching "&lt;term&gt;"'.</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>The 'No countries found matching...' empty-state message correctly appeared.</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'No countries found matching...' message is shown</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_17</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Clearing the country search box restores the full list</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>After filtering to 'Austra' and then clearing the search box, the full country list (including Bangladesh) must reappear.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Search 'Austra'
+3. Clear the search box
+4. Verify Bangladesh reappears</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>After filtering to 'Austra' and then clearing the search box, the full country list (including Bangladesh) must reappear.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Clearing the country search box correctly restored the full country list.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Bangladesh reappears after clearing the country search</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>LANDING_18</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Searching categories filters the category tree</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Typing 'Liability' in the category search box must show 'Liability to Tax' and hide non-matching categories (e.g. 'Tax Compliance').</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Search term: Liability</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Type 'Liability' into the category search box
 3. Verify 'Liability to Tax' is shown and 'Tax Compliance' is hidden</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Typing 'Liability' in the category search box must show 'Liability to Tax' and hide non-matching categories (e.g. 'Tax Compliance').</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>Searching 'Liability' correctly filtered the category tree.</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Liability to Tax' is shown and 'Tax Compliance' is hidden after searching 'Liability'</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>LANDING_19</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Searching for a non-existent category shows 'No results found.'</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Typing a term that matches no category must show 'No results found.' - note this wording differs from the country search's empty state, which echoes the search term.</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Search term: zzznotreal</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Type 'zzznotreal' into the category search box
 3. Verify 'No results found.' appears</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Typing a term that matches no category must show 'No results found.' - note this wording differs from the country search's empty state, which echoes the search term.</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>The 'No results found.' empty-state message correctly appeared for the category search.</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'No results found.' message is shown</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>LANDING_20</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Clearing the category search box restores the full tree</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>After filtering to 'Liability' and then clearing the search box, the full category tree (including 'Tax Compliance') must reappear.</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Search 'Liability'
@@ -1382,117 +1669,176 @@
 4. Verify 'Tax Compliance' reappears</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>After filtering to 'Liability' and then clearing the search box, the full category tree (including 'Tax Compliance') must reappear.</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>Clearing the category search box correctly restored the full category tree.</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Tax Compliance' reappears after clearing the category search</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>LANDING_21</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>'Check All' (categories) is unchecked by default</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>On first load, the 'Check All' category checkbox must be unchecked.</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Verify the 'Check All' checkbox is unchecked</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>On first load, the 'Check All' category checkbox must be unchecked.</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>'Check All' was not unchecked by default (state: None).</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>[FAIL] 'Check All' checkbox is unchecked by default</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>'Check All' is unchecked by default, as expected.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Check All' checkbox is unchecked by default</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_22</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>'Check All' checks every top-level category</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Check All' must check every top-level category, e.g. 'Liability to Tax'.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page, 'Check All' unchecked.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click 'Check All'
+3. Verify 'Liability to Tax' becomes checked</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Check All' must check every top-level category, e.g. 'Liability to Tax'.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Check All' correctly cascaded to check every top-level category.</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Check All' and 'Liability to Tax' are both checked after clicking 'Check All'</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>LANDING_23</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Unchecking 'Check All' unchecks every category again</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>After checking 'Check All', clicking it again must uncheck every category, e.g. 'Liability to Tax'.</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click 'Check All' to check it
@@ -1500,59 +1846,119 @@
 4. Verify 'Liability to Tax' is unchecked</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>After checking 'Check All', clicking it again must uncheck every category, e.g. 'Liability to Tax'.</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>Toggling 'Check All' off correctly unchecked every category.</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Check All' and 'Liability to Tax' are both unchecked after toggling 'Check All' off</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_24</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Depth control expands the visible category tree</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Clicking Depth level '4' must reveal substantially more nested category content than the default view (confirmed live: default/1 ~585 characters of panel text vs. depth 4 ~3519 characters).</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Depth level: 4</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Record the category panel's text length
+3. Click Depth '4'
+4. Verify the panel's text length increased substantially</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Clicking Depth level '4' must reveal substantially more nested category content than the default view (confirmed live: default/1 ~585 characters of panel text vs. depth 4 ~3519 characters).</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Selecting Depth '4' expanded the category panel from 585 to 3519 characters of visible content.</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Category panel text length roughly doubles or more after selecting Depth 4</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>LANDING_25</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Selecting a second country keeps the first one checked</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Checking 'Australia' then 'Bangladesh' must leave both checked - the jurisdiction panel supports multi-select.</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Countries: Australia, Bangladesh</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Check 'Australia'
@@ -1560,177 +1966,296 @@
 4. Verify both remain checked</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Checking 'Australia' then 'Bangladesh' must leave both checked - the jurisdiction panel supports multi-select.</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>The jurisdiction panel correctly supports multi-select: both Australia and Bangladesh remained checked.</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>[PASS] Both 'Australia' and 'Bangladesh' remain checked (multi-select)</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Deselecting a checked country unchecks it</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Checking then re-clicking 'Australia' must uncheck it.</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Check 'Australia'
+3. Click 'Australia' again to uncheck it
+4. Verify it is unchecked</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Checking then re-clicking 'Australia' must uncheck it.</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Australia' a second time correctly unchecked it.</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Australia' is unchecked after clicking it a second time</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>LANDING_27</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>'Workspace' product tab navigates to the Companydata dashboard</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Clicking the 'Workspace' tab must navigate to /companydata/dashboard/ - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click the 'Workspace' tab
 3. Verify the URL is /companydata/dashboard/</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Clicking the 'Workspace' tab must navigate to /companydata/dashboard/ - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Workspace' navigated to https://regplus.reganalytics.com/companydata/dashboard/, the Companydata dashboard.</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Workspace' navigated to https://regplus.kaz.com.bd/companydata/dashboard/, the Companydata dashboard.</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>[PASS] URL contains /companydata/dashboard/</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>LANDING_28</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>'Transfer Pricing Analyzer' tab navigates to the TPA module</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Clicking the 'Transfer Pricing Analyzer' tab must navigate to /tpa/Home - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click the 'Transfer Pricing Analyzer' tab
 3. Verify the URL is /tpa/Home</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Clicking the 'Transfer Pricing Analyzer' tab must navigate to /tpa/Home - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Transfer Pricing Analyzer' navigated to https://regplus.reganalytics.com/tpa/Home.</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Transfer Pricing Analyzer' navigated to https://regplus.kaz.com.bd/tpa/Home.</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>[PASS] URL contains /tpa/Home</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_29</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>'RegBriefings' tab navigates to the RegBriefings module</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the 'RegBriefings' tab must navigate to /regbrief/home/ - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click the 'RegBriefings' tab
+3. Verify the URL contains /regbrief/home/</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the 'RegBriefings' tab must navigate to /regbrief/home/ - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'RegBriefings' navigated to https://regplus.kaz.com.bd/regbrief/home/myBriefings.</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] URL contains /regbrief/home/</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>LANDING_30</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Browser back navigation returns from News to Information</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>After navigating to News via the top nav, using the browser's back button must return to /wta/Information.</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click 'News'
@@ -1738,548 +2263,724 @@
 4. Verify the URL is /wta/Information</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>After navigating to News via the top nav, using the browser's back button must return to /wta/Information.</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Browser back correctly returned to https://regplus.reganalytics.com/wta/Information.</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Browser back correctly returned to https://regplus.kaz.com.bd/wta/Information.</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>[PASS] Browser back returns to /wta/Information</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>LANDING_31</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Reloading the page preserves the authenticated session</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Reloading /wta/Information (F5) must keep the user authenticated and on the same page, not bounce them to the login page.</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Reload the page
 3. Verify the user is still on /wta/Information, not redirected to /auth/login</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Reloading /wta/Information (F5) must keep the user authenticated and on the same page, not bounce them to the login page.</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Reloading the page correctly preserved the authenticated session; still on https://regplus.reganalytics.com/wta/Information.</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Reloading the page correctly preserved the authenticated session; still on https://regplus.kaz.com.bd/wta/Information.</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>[PASS] User remains on /wta/Information after reload (not redirected to login)</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>LANDING_32</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>The content placeholder is shown before any selection</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Before selecting a jurisdiction or category, the right panel must show 'Select Jurisdictions and Categories'.</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on the landing page, nothing selected.</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Verify the 'Select Jurisdictions and Categories' placeholder is visible</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Before selecting a jurisdiction or category, the right panel must show 'Select Jurisdictions and Categories'.</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>The expected placeholder text was not visible.</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>[FAIL] Placeholder text is visible before any selection</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>The 'Select Jurisdictions and Categories' placeholder is correctly shown before any selection.</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Placeholder text is visible before any selection</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_33</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Exactly 4 region tabs are present</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>The jurisdiction panel must show exactly 4 region tabs: Asia Pacific, Americas, Europe, MEA - no more, no fewer.</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify exactly 4 region tabs are present</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>The jurisdiction panel must show exactly 4 region tabs: Asia Pacific, Americas, Europe, MEA - no more, no fewer.</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Exactly the 4 expected region tabs (Asia Pacific, Americas, Europe, MEA) are present.</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Each of the 4 region tabs appears exactly once</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>LANDING_34</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Asia Pacific region shows the expected number of countries</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>The Asia Pacific region (default) must list 25 countries, confirmed live (Australia through Vietnam).</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on the landing page, Asia Pacific active.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Count the visible country checkboxes in the Asia Pacific list
 3. Verify the count is 25</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>The Asia Pacific region (default) must list 25 countries, confirmed live (Australia through Vietnam).</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>Asia Pacific correctly lists 25 countries.</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>[PASS] Asia Pacific lists exactly 25 countries</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>LANDING_35</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Exactly the 5 expected main nav items are present</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>The top nav must show Information, Pillar 2, News, Forms and Regulations - no more, no fewer.</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Verify each of the 5 main nav items appears exactly once</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>The top nav must show Information, Pillar 2, News, Forms and Regulations - no more, no fewer.</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>Exactly the 5 expected main nav items are present.</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>[PASS] Each of the 5 main nav items appears exactly once</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>LANDING_36</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Expected top-level categories are present in the tree</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>The category tree's default view must include the top-level categories 'Liability to Tax' and 'Tax Compliance'.</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Verify 'Liability to Tax' and 'Tax Compliance' are visible</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>The category tree's default view must include the top-level categories 'Liability to Tax' and 'Tax Compliance'.</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>Missing expected categories: Liability to Tax=False, Tax Compliance=False.</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>[FAIL] 'Liability to Tax' and 'Tax Compliance' are both visible</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Both expected top-level categories are visible in the default tree view.</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Liability to Tax' and 'Tax Compliance' are both visible</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>LANDING_37</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Exactly 4 product tabs are present</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>The product-tab row must show Workspace, World Tax Analyzer, Transfer Pricing Analyzer and RegBriefings - no more, no fewer.</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Verify each of the 4 product tabs appears exactly once</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>The product-tab row must show Workspace, World Tax Analyzer, Transfer Pricing Analyzer and RegBriefings - no more, no fewer.</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>Exactly the 4 expected product tabs are present.</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>[PASS] Each of the 4 product tabs appears exactly once</t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>LANDING_38</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>A single category can be checked without using 'Check All'</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Liability to Tax's checkbox directly must check it, while 'Check All' remains unchecked (it only reflects when every category is checked). Note: the category LABEL text has no 'for' attribute linking it to its checkbox (confirmed live) - clicking the label is a no-op; only the checkbox input itself (or 'Check All', which has its own working handler) toggles selection.</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Category: Liability to Tax</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click 'Liability to Tax's checkbox
 3. Verify it is checked and 'Check All' remains unchecked</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Liability to Tax's checkbox directly must check it, while 'Check All' remains unchecked (it only reflects when every category is checked). Note: the category LABEL text has no 'for' attribute linking it to its checkbox (confirmed live) - clicking the label is a no-op; only the checkbox input itself (or 'Check All', which has its own working handler) toggles selection.</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>A single category can be selected independently of 'Check All'.</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Liability to Tax' is checked while 'Check All' remains unchecked</t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_39</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Special-character input in the country search doesn't error</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Typing special characters into the country search box must be handled gracefully (the same 'No countries found...' empty state, no crash).</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Search term: @@@###$$$</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Type '@@@###$$$' into the country search box
+3. Verify the page does not error and shows the no-match message</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Typing special characters into the country search box must be handled gracefully (the same 'No countries found...' empty state, no crash).</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Special-character input was handled gracefully with the expected empty-state message.</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Special-character search shows the no-match message without breaking the panel</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_40</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Special-character input in the category search doesn't error</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Typing special characters into the category search box must be handled gracefully (the same 'No results found.' empty state, no crash).</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Search term: @@@###$$$</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Type '@@@###$$$' into the category search box
+3. Verify the page does not error and shows 'No results found.'</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Typing special characters into the category search box must be handled gracefully (the same 'No results found.' empty state, no crash).</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Special-character input was handled gracefully with the expected empty-state message.</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Special-character search shows 'No results found.' without breaking the panel</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>LANDING_41</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>'World Tax Analyzer' tab keeps the user within WTA</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Clicking the already-active 'World Tax Analyzer' product tab must not navigate away from the WTA module.</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on the landing page (WTA already active).</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click the 'World Tax Analyzer' tab
 3. Verify the URL is still within /wta/</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Clicking the already-active 'World Tax Analyzer' product tab must not navigate away from the WTA module.</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>Clicking the already-active 'World Tax Analyzer' tab correctly kept the user within WTA, at https://regplus.reganalytics.com/wta/Information.</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the already-active 'World Tax Analyzer' tab correctly kept the user within WTA, at https://regplus.kaz.com.bd/wta/Information.</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>[PASS] URL remains within /wta/ after clicking the already-active tab</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>LANDING_42</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>'Information' nav link points to /wta/Information</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>The 'Information' nav link's href must point to /wta/Information, consistent with it being the post-login landing page.</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Verify the 'Information' nav link's href</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>The 'Information' nav link's href must point to /wta/Information, consistent with it being the post-login landing page.</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr">
         <is>
           <t>'Information' nav link correctly points to /wta/Information.</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J43" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Information' nav link href contains /wta/Information</t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
+      <c r="K43" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/Dashboard/Dashboard_Test_Cases.xlsx
+++ b/test_data/Dashboard/Dashboard_Test_Cases.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +47,11 @@
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -60,7 +65,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -69,6 +74,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -436,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,7 +520,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>LANDING_01</t>
+          <t>LANDING_03</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,44 +530,44 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Landing page loads after a successful login</t>
+          <t>Clicking the News nav link navigates to the News module</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>After login the app must land on the World Tax Analyzer Information workspace with the jurisdiction/category panel visible.</t>
+          <t>Clicking 'News' in the top nav must navigate to /wta/News.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Valid credentials are used to log in.</t>
+          <t>User is logged in and on the landing page.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Email: demo@reganalytics.com / Password: &lt;masked&gt;</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. Log in with valid credentials
-2. Verify the URL is /wta/Information
-3. Verify the 'Jurisdictions and Categories' panel is visible</t>
+          <t>1. Log in
+2. Click 'News' in the top navigation
+3. Verify the URL is /wta/News</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>After login the app must land on the World Tax Analyzer Information workspace with the jurisdiction/category panel visible.</t>
+          <t>Clicking 'News' in the top nav must navigate to /wta/News.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>After login the app landed on https://regplus.kaz.com.bd/wta/Information with the 'Jurisdictions and Categories' panel visible.</t>
+          <t>Clicking 'News' navigated to https://regplusrc.reganalytics.com/wta/News.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[PASS] URL is /wta/Information and the Jurisdictions panel is visible</t>
+          <t>[PASS] URL contains /wta/News</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -571,7 +579,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>LANDING_02</t>
+          <t>LANDING_04</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -581,17 +589,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Top navigation and product tabs are visible</t>
+          <t>The cookie consent banner can be dismissed</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>The main module nav (Information/News/Forms/Regulations) and the product tabs (Workspace/World Tax Analyzer/Transfer Pricing Analyzer/RegBriefings) must be visible on the landing page.</t>
+          <t>The 'Please review our Terms and Conditions...' banner must disappear after clicking Accept.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on the landing page.</t>
+          <t>User is logged in; the cookie banner is showing (first session load).</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -600,124 +608,6 @@
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Verify each nav link and product tab is visible</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>The main module nav (Information/News/Forms/Regulations) and the product tabs (Workspace/World Tax Analyzer/Transfer Pricing Analyzer/RegBriefings) must be visible on the landing page.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>All main navigation links (Information, News, Forms, Regulations) and product tabs (Workspace, World Tax Analyzer, Transfer Pricing Analyzer, RegBriefings) are visible.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Information/News/Forms/Regulations links are visible
-[PASS] Workspace/World Tax Analyzer/Transfer Pricing Analyzer/RegBriefings tabs are visible</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>LANDING_03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Clicking the News nav link navigates to the News module</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'News' in the top nav must navigate to /wta/News.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Click 'News' in the top navigation
-3. Verify the URL is /wta/News</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'News' in the top nav must navigate to /wta/News.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'News' navigated to https://regplus.kaz.com.bd/wta/News.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] URL contains /wta/News</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>LANDING_04</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>The cookie consent banner can be dismissed</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>The 'Please review our Terms and Conditions...' banner must disappear after clicking Accept.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in; the cookie banner is showing (first session load).</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Verify the cookie banner is visible
@@ -725,19 +615,137 @@
 4. Verify the banner is no longer visible</t>
         </is>
       </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>The 'Please review our Terms and Conditions...' banner must disappear after clicking Accept.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Clicking Accept dismissed the cookie banner.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Cookie banner is no longer visible after Accept</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_05</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Selecting a jurisdiction checks its checkbox</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Clicking a country in the Jurisdictions panel (e.g. Australia) must check its checkbox, confirming the left panel is interactive.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page, Asia Pacific region selected by default.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click the 'Australia' checkbox in the Jurisdictions panel
+3. Verify the checkbox becomes checked</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Clicking a country in the Jurisdictions panel (e.g. Australia) must check its checkbox, confirming the left panel is interactive.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Australia' in the Jurisdictions panel checked its checkbox, confirming the panel responds to selection.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Australia's checkbox is checked after clicking it</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_06</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the Forms nav link navigates to the Forms module</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Forms' in the top nav must navigate to /wta/Forms.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Click 'Forms' in the top navigation
+3. Verify the URL is /wta/Forms</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>The 'Please review our Terms and Conditions...' banner must disappear after clicking Accept.</t>
+          <t>Clicking 'Forms' in the top nav must navigate to /wta/Forms.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Clicking Accept dismissed the cookie banner.</t>
+          <t>Clicking 'Forms' navigated to https://regplusrc.reganalytics.com/wta/Forms.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Cookie banner is no longer visible after Accept</t>
+          <t>[PASS] URL contains /wta/Forms</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -749,7 +757,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>LANDING_05</t>
+          <t>LANDING_07</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -759,44 +767,44 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Selecting a jurisdiction checks its checkbox</t>
+          <t>Clicking the Regulations nav link navigates to the Regulations module</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Clicking a country in the Jurisdictions panel (e.g. Australia) must check its checkbox, confirming the left panel is interactive.</t>
+          <t>Clicking 'Regulations' in the top nav must navigate to /wta/Regulations.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on the landing page, Asia Pacific region selected by default.</t>
+          <t>User is logged in and on the landing page.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Country: Australia</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1. Log in
-2. Click the 'Australia' checkbox in the Jurisdictions panel
-3. Verify the checkbox becomes checked</t>
+2. Click 'Regulations' in the top navigation
+3. Verify the URL is /wta/Regulations</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Clicking a country in the Jurisdictions panel (e.g. Australia) must check its checkbox, confirming the left panel is interactive.</t>
+          <t>Clicking 'Regulations' in the top nav must navigate to /wta/Regulations.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Australia' in the Jurisdictions panel checked its checkbox, confirming the panel responds to selection.</t>
+          <t>Clicking 'Regulations' navigated to https://regplusrc.reganalytics.com/wta/Regulations.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Australia's checkbox is checked after clicking it</t>
+          <t>[PASS] URL contains /wta/Regulations</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -808,7 +816,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>LANDING_06</t>
+          <t>LANDING_10</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -818,17 +826,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Clicking the Forms nav link navigates to the Forms module</t>
+          <t>Switching to the Americas region tab swaps the country list</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Forms' in the top nav must navigate to /wta/Forms.</t>
+          <t>Clicking 'Americas' must show Americas countries (e.g. Brazil) and hide Asia Pacific countries (e.g. Australia).</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on the landing page.</t>
+          <t>User is logged in and on the landing page, Asia Pacific selected by default.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -839,23 +847,23 @@
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1. Log in
-2. Click 'Forms' in the top navigation
-3. Verify the URL is /wta/Forms</t>
+2. Click the 'Americas' region tab
+3. Verify Brazil is shown and Australia is hidden</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Forms' in the top nav must navigate to /wta/Forms.</t>
+          <t>Clicking 'Americas' must show Americas countries (e.g. Brazil) and hide Asia Pacific countries (e.g. Australia).</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Forms' navigated to https://regplus.kaz.com.bd/wta/Forms.</t>
+          <t>Switching to Americas correctly swapped the country list.</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>[PASS] URL contains /wta/Forms</t>
+          <t>[PASS] Brazil (Americas) is visible and Australia (Asia Pacific) is not</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -867,7 +875,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>LANDING_07</t>
+          <t>LANDING_11</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -877,12 +885,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Clicking the Regulations nav link navigates to the Regulations module</t>
+          <t>Switching to the Europe region tab swaps the country list</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Regulations' in the top nav must navigate to /wta/Regulations.</t>
+          <t>Clicking 'Europe' must show Europe countries (e.g. France) and hide Asia Pacific countries (e.g. Australia).</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -898,23 +906,23 @@
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1. Log in
-2. Click 'Regulations' in the top navigation
-3. Verify the URL is /wta/Regulations</t>
+2. Click the 'Europe' region tab
+3. Verify France is shown and Australia is hidden</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Regulations' in the top nav must navigate to /wta/Regulations.</t>
+          <t>Clicking 'Europe' must show Europe countries (e.g. France) and hide Asia Pacific countries (e.g. Australia).</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Regulations' navigated to https://regplus.kaz.com.bd/wta/Regulations.</t>
+          <t>Switching to Europe correctly swapped the country list.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>[PASS] URL contains /wta/Regulations</t>
+          <t>[PASS] France (Europe) is visible and Australia (Asia Pacific) is not</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -926,7 +934,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>LANDING_08</t>
+          <t>LANDING_12</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -936,12 +944,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>'Pillar 2' nav button is visible and enabled</t>
+          <t>Switching to the MEA region tab swaps the country list</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>The 'Pillar 2' dropdown trigger in the top nav must be visible and enabled. Its dropdown contents are covered in depth by the WTA Pillar2 Menu module - this is a light presence check only, to avoid duplicating that coverage.</t>
+          <t>Clicking 'MEA' must show MEA countries (e.g. Egypt) and hide Asia Pacific countries (e.g. Australia).</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -957,22 +965,23 @@
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t>1. Log in
-2. Verify the 'Pillar 2' nav button is visible and enabled</t>
+2. Click the 'MEA' region tab
+3. Verify Egypt is shown and Australia is hidden</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>The 'Pillar 2' dropdown trigger in the top nav must be visible and enabled. Its dropdown contents are covered in depth by the WTA Pillar2 Menu module - this is a light presence check only, to avoid duplicating that coverage.</t>
+          <t>Clicking 'MEA' must show MEA countries (e.g. Egypt) and hide Asia Pacific countries (e.g. Australia).</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>The 'Pillar 2' nav button is visible and enabled.</t>
+          <t>Switching to MEA correctly swapped the country list.</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>[PASS] 'Pillar 2' nav button is visible and enabled</t>
+          <t>[PASS] Egypt (MEA) is visible and Australia (Asia Pacific) is not</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -984,7 +993,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>LANDING_09</t>
+          <t>LANDING_13</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -994,17 +1003,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>'Asia Pacific' region tab is selected by default</t>
+          <t>Clicking a region tab activates it and deactivates the previous one</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>On first load, the 'Asia Pacific' region tab must carry the active/selected styling and 'Americas' must not.</t>
+          <t>After clicking 'Americas', it must carry the active/selected styling and 'Asia Pacific' must no longer carry it.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on the landing page.</t>
+          <t>User is logged in and on the landing page, Asia Pacific active by default.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1015,22 +1024,23 @@
       <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1. Log in
-2. Verify 'Asia Pacific' is the active region tab</t>
+2. Click the 'Americas' region tab
+3. Verify Americas is now active and Asia Pacific is not</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>On first load, the 'Asia Pacific' region tab must carry the active/selected styling and 'Americas' must not.</t>
+          <t>After clicking 'Americas', it must carry the active/selected styling and 'Asia Pacific' must no longer carry it.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>'Asia Pacific' is the default active region tab.</t>
+          <t>Clicking 'Americas' correctly toggled the active region tab.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>[PASS] 'Asia Pacific' is active and 'Americas' is not, by default</t>
+          <t>[PASS] 'Americas' is now active and 'Asia Pacific' is not</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -1042,7 +1052,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>LANDING_10</t>
+          <t>LANDING_14</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1052,44 +1062,44 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Switching to the Americas region tab swaps the country list</t>
+          <t>Searching countries filters the jurisdiction checklist</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Americas' must show Americas countries (e.g. Brazil) and hide Asia Pacific countries (e.g. Australia).</t>
+          <t>Typing 'Austra' in the country search box must show Australia and hide non-matching countries (e.g. Bangladesh).</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on the landing page, Asia Pacific selected by default.</t>
+          <t>User is logged in and on the landing page, Asia Pacific region active.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Search term: Austra</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1. Log in
-2. Click the 'Americas' region tab
-3. Verify Brazil is shown and Australia is hidden</t>
+2. Type 'Austra' into the country search box
+3. Verify Australia is shown and Bangladesh is hidden</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Americas' must show Americas countries (e.g. Brazil) and hide Asia Pacific countries (e.g. Australia).</t>
+          <t>Typing 'Austra' in the country search box must show Australia and hide non-matching countries (e.g. Bangladesh).</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Switching to Americas correctly swapped the country list.</t>
+          <t>Searching 'Austra' correctly filtered the country list.</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Brazil (Americas) is visible and Australia (Asia Pacific) is not</t>
+          <t>[PASS] Australia is shown and Bangladesh is hidden after searching 'Austra'</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -1101,7 +1111,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>LANDING_11</t>
+          <t>LANDING_15</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1111,12 +1121,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Switching to the Europe region tab swaps the country list</t>
+          <t>Country search is case-insensitive</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Europe' must show Europe countries (e.g. France) and hide Asia Pacific countries (e.g. Australia).</t>
+          <t>Typing a lowercase search term ('austra') must still match 'Australia'.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1126,29 +1136,29 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Search term: austra (lowercase)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1. Log in
-2. Click the 'Europe' region tab
-3. Verify France is shown and Australia is hidden</t>
+2. Type 'austra' (lowercase) into the country search box
+3. Verify Australia is still shown</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Europe' must show Europe countries (e.g. France) and hide Asia Pacific countries (e.g. Australia).</t>
+          <t>Typing a lowercase search term ('austra') must still match 'Australia'.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Switching to Europe correctly swapped the country list.</t>
+          <t>Country search is case-insensitive: 'austra' matched Australia.</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>[PASS] France (Europe) is visible and Australia (Asia Pacific) is not</t>
+          <t>[PASS] Australia is shown for the lowercase search 'austra'</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
@@ -1160,7 +1170,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>LANDING_12</t>
+          <t>LANDING_16</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1170,12 +1180,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Switching to the MEA region tab swaps the country list</t>
+          <t>Searching for a non-existent country shows a 'no results' message</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'MEA' must show MEA countries (e.g. Egypt) and hide Asia Pacific countries (e.g. Australia).</t>
+          <t>Typing a term that matches no country must show 'No countries found matching "&lt;term&gt;"'.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1185,29 +1195,29 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Search term: zzzznotreal</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1. Log in
-2. Click the 'MEA' region tab
-3. Verify Egypt is shown and Australia is hidden</t>
+2. Type 'zzzznotreal' into the country search box
+3. Verify the 'No countries found matching...' message appears</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'MEA' must show MEA countries (e.g. Egypt) and hide Asia Pacific countries (e.g. Australia).</t>
+          <t>Typing a term that matches no country must show 'No countries found matching "&lt;term&gt;"'.</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Switching to MEA correctly swapped the country list.</t>
+          <t>The 'No countries found matching...' empty-state message correctly appeared.</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Egypt (MEA) is visible and Australia (Asia Pacific) is not</t>
+          <t>[PASS] 'No countries found matching...' message is shown</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -1219,7 +1229,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>LANDING_13</t>
+          <t>LANDING_17</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1229,17 +1239,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Clicking a region tab activates it and deactivates the previous one</t>
+          <t>Clearing the country search box restores the full list</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>After clicking 'Americas', it must carry the active/selected styling and 'Asia Pacific' must no longer carry it.</t>
+          <t>After filtering to 'Austra' and then clearing the search box, the full country list (including Bangladesh) must reappear.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on the landing page, Asia Pacific active by default.</t>
+          <t>User is logged in and on the landing page.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1248,242 +1258,6 @@
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Click the 'Americas' region tab
-3. Verify Americas is now active and Asia Pacific is not</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>After clicking 'Americas', it must carry the active/selected styling and 'Asia Pacific' must no longer carry it.</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Americas' correctly toggled the active region tab.</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'Americas' is now active and 'Asia Pacific' is not</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>LANDING_14</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Searching countries filters the jurisdiction checklist</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Typing 'Austra' in the country search box must show Australia and hide non-matching countries (e.g. Bangladesh).</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page, Asia Pacific region active.</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Search term: Austra</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Type 'Austra' into the country search box
-3. Verify Australia is shown and Bangladesh is hidden</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Typing 'Austra' in the country search box must show Australia and hide non-matching countries (e.g. Bangladesh).</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Searching 'Austra' correctly filtered the country list.</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Australia is shown and Bangladesh is hidden after searching 'Austra'</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>LANDING_15</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Country search is case-insensitive</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Typing a lowercase search term ('austra') must still match 'Australia'.</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Search term: austra (lowercase)</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Type 'austra' (lowercase) into the country search box
-3. Verify Australia is still shown</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Typing a lowercase search term ('austra') must still match 'Australia'.</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Country search is case-insensitive: 'austra' matched Australia.</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Australia is shown for the lowercase search 'austra'</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>LANDING_16</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Searching for a non-existent country shows a 'no results' message</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Typing a term that matches no country must show 'No countries found matching "&lt;term&gt;"'.</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Search term: zzzznotreal</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Type 'zzzznotreal' into the country search box
-3. Verify the 'No countries found matching...' message appears</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Typing a term that matches no country must show 'No countries found matching "&lt;term&gt;"'.</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>The 'No countries found matching...' empty-state message correctly appeared.</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'No countries found matching...' message is shown</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>LANDING_17</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Clearing the country search box restores the full list</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>After filtering to 'Austra' and then clearing the search box, the full country list (including Bangladesh) must reappear.</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Search 'Austra'
@@ -1491,177 +1265,177 @@
 4. Verify Bangladesh reappears</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>After filtering to 'Austra' and then clearing the search box, the full country list (including Bangladesh) must reappear.</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Clearing the country search box correctly restored the full country list.</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>[PASS] Bangladesh reappears after clearing the country search</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>LANDING_18</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Searching categories filters the category tree</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Typing 'Liability' in the category search box must show 'Liability to Tax' and hide non-matching categories (e.g. 'Tax Compliance').</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Search term: Liability</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Type 'Liability' into the category search box
 3. Verify 'Liability to Tax' is shown and 'Tax Compliance' is hidden</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Typing 'Liability' in the category search box must show 'Liability to Tax' and hide non-matching categories (e.g. 'Tax Compliance').</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>Searching 'Liability' correctly filtered the category tree.</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Liability to Tax' is shown and 'Tax Compliance' is hidden after searching 'Liability'</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>LANDING_19</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Searching for a non-existent category shows 'No results found.'</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Typing a term that matches no category must show 'No results found.' - note this wording differs from the country search's empty state, which echoes the search term.</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Search term: zzznotreal</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Type 'zzznotreal' into the category search box
 3. Verify 'No results found.' appears</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Typing a term that matches no category must show 'No results found.' - note this wording differs from the country search's empty state, which echoes the search term.</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>The 'No results found.' empty-state message correctly appeared for the category search.</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'No results found.' message is shown</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>LANDING_20</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Clearing the category search box restores the full tree</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>After filtering to 'Liability' and then clearing the search box, the full category tree (including 'Tax Compliance') must reappear.</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Search 'Liability'
@@ -1669,176 +1443,118 @@
 4. Verify 'Tax Compliance' reappears</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>After filtering to 'Liability' and then clearing the search box, the full category tree (including 'Tax Compliance') must reappear.</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>Clearing the category search box correctly restored the full category tree.</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Tax Compliance' reappears after clearing the category search</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>LANDING_21</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>'Check All' (categories) is unchecked by default</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>On first load, the 'Check All' category checkbox must be unchecked.</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_22</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>'Check All' checks every top-level category</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Check All' must check every top-level category, e.g. 'Liability to Tax'.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page, 'Check All' unchecked.</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Verify the 'Check All' checkbox is unchecked</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>On first load, the 'Check All' category checkbox must be unchecked.</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>'Check All' is unchecked by default, as expected.</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'Check All' checkbox is unchecked by default</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>LANDING_22</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>'Check All' checks every top-level category</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Check All' must check every top-level category, e.g. 'Liability to Tax'.</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page, 'Check All' unchecked.</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click 'Check All'
 3. Verify 'Liability to Tax' becomes checked</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Check All' must check every top-level category, e.g. 'Liability to Tax'.</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Check All' correctly cascaded to check every top-level category.</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Check All' and 'Liability to Tax' are both checked after clicking 'Check All'</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>LANDING_23</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Unchecking 'Check All' unchecks every category again</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>After checking 'Check All', clicking it again must uncheck every category, e.g. 'Liability to Tax'.</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click 'Check All' to check it
@@ -1846,59 +1562,59 @@
 4. Verify 'Liability to Tax' is unchecked</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>After checking 'Check All', clicking it again must uncheck every category, e.g. 'Liability to Tax'.</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>Toggling 'Check All' off correctly unchecked every category.</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Check All' and 'Liability to Tax' are both unchecked after toggling 'Check All' off</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>LANDING_24</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Depth control expands the visible category tree</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Clicking Depth level '4' must reveal substantially more nested category content than the default view (confirmed live: default/1 ~585 characters of panel text vs. depth 4 ~3519 characters).</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Depth level: 4</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Record the category panel's text length
@@ -1906,59 +1622,59 @@
 4. Verify the panel's text length increased substantially</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Clicking Depth level '4' must reveal substantially more nested category content than the default view (confirmed live: default/1 ~585 characters of panel text vs. depth 4 ~3519 characters).</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>Selecting Depth '4' expanded the category panel from 585 to 3519 characters of visible content.</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Selecting Depth '4' expanded the category panel from 554 to 3114 characters of visible content.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>[PASS] Category panel text length roughly doubles or more after selecting Depth 4</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>LANDING_25</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Selecting a second country keeps the first one checked</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Checking 'Australia' then 'Bangladesh' must leave both checked - the jurisdiction panel supports multi-select.</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Countries: Australia, Bangladesh</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Check 'Australia'
@@ -1966,59 +1682,59 @@
 4. Verify both remain checked</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Checking 'Australia' then 'Bangladesh' must leave both checked - the jurisdiction panel supports multi-select.</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>The jurisdiction panel correctly supports multi-select: both Australia and Bangladesh remained checked.</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>[PASS] Both 'Australia' and 'Bangladesh' remain checked (multi-select)</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>LANDING_26</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Deselecting a checked country unchecks it</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Checking then re-clicking 'Australia' must uncheck it.</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Country: Australia</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Check 'Australia'
@@ -2026,236 +1742,236 @@
 4. Verify it is unchecked</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Checking then re-clicking 'Australia' must uncheck it.</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Australia' a second time correctly unchecked it.</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Australia' is unchecked after clicking it a second time</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>LANDING_27</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>'Workspace' product tab navigates to the Companydata dashboard</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Clicking the 'Workspace' tab must navigate to /companydata/dashboard/ - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click the 'Workspace' tab
 3. Verify the URL is /companydata/dashboard/</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Clicking the 'Workspace' tab must navigate to /companydata/dashboard/ - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Workspace' navigated to https://regplus.kaz.com.bd/companydata/dashboard/, the Companydata dashboard.</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Workspace' navigated to https://regplusrc.reganalytics.com/companydata/dashboard/, the Companydata dashboard.</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>[PASS] URL contains /companydata/dashboard/</t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>LANDING_28</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>'Transfer Pricing Analyzer' tab navigates to the TPA module</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Clicking the 'Transfer Pricing Analyzer' tab must navigate to /tpa/Home - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click the 'Transfer Pricing Analyzer' tab
 3. Verify the URL is /tpa/Home</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Clicking the 'Transfer Pricing Analyzer' tab must navigate to /tpa/Home - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Transfer Pricing Analyzer' navigated to https://regplus.kaz.com.bd/tpa/Home.</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Transfer Pricing Analyzer' navigated to https://regplusrc.reganalytics.com/tpa/Home.</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>[PASS] URL contains /tpa/Home</t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>LANDING_29</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>'RegBriefings' tab navigates to the RegBriefings module</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Clicking the 'RegBriefings' tab must navigate to /regbrief/home/ - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click the 'RegBriefings' tab
 3. Verify the URL contains /regbrief/home/</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Clicking the 'RegBriefings' tab must navigate to /regbrief/home/ - a different product area, out of this suite's WTA scope. Covered here only as a navigation smoke check.</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'RegBriefings' navigated to https://regplus.kaz.com.bd/regbrief/home/myBriefings.</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'RegBriefings' navigated to https://regplusrc.reganalytics.com/regbrief/home/myBriefings.</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>[PASS] URL contains /regbrief/home/</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>LANDING_30</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Browser back navigation returns from News to Information</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>After navigating to News via the top nav, using the browser's back button must return to /wta/Information.</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click 'News'
@@ -2263,19 +1979,311 @@
 4. Verify the URL is /wta/Information</t>
         </is>
       </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>After navigating to News via the top nav, using the browser's back button must return to /wta/Information.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Browser back correctly returned to https://regplusrc.reganalytics.com/wta/Information.</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Browser back returns to /wta/Information</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_31</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Reloading the page preserves the authenticated session</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Reloading /wta/Information (F5) must keep the user authenticated and on the same page, not bounce them to the login page.</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Reload the page
+3. Verify the user is still on /wta/Information, not redirected to /auth/login</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Reloading /wta/Information (F5) must keep the user authenticated and on the same page, not bounce them to the login page.</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Reloading the page correctly preserved the authenticated session; still on https://regplusrc.reganalytics.com/wta/Information.</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] User remains on /wta/Information after reload (not redirected to login)</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_33</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Exactly 4 region tabs are present</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>The jurisdiction panel must show exactly 4 region tabs: Asia Pacific, Americas, Europe, MEA - no more, no fewer.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify exactly 4 region tabs are present</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>The jurisdiction panel must show exactly 4 region tabs: Asia Pacific, Americas, Europe, MEA - no more, no fewer.</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Exactly the 4 expected region tabs (Asia Pacific, Americas, Europe, MEA) are present.</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Each of the 4 region tabs appears exactly once</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_34</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Asia Pacific region shows the expected number of countries</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>The Asia Pacific region (default) must list 25 countries, confirmed live (Australia through Vietnam).</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page, Asia Pacific active.</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Count the visible country checkboxes in the Asia Pacific list
+3. Verify the count is 25</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>The Asia Pacific region (default) must list 25 countries, confirmed live (Australia through Vietnam).</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Expected 25 countries in Asia Pacific, found 22.</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>[FAIL] Asia Pacific lists exactly 25 countries</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_35</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Exactly the 5 expected main nav items are present</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>The top nav must show Information, Pillar 2, News, Forms and Regulations - no more, no fewer.</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify each of the 5 main nav items appears exactly once</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>The top nav must show Information, Pillar 2, News, Forms and Regulations - no more, no fewer.</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Exactly the 5 expected main nav items are present.</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Each of the 5 main nav items appears exactly once</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_36</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Expected top-level categories are present in the tree</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>The category tree's default view must include the top-level categories 'Liability to Tax' and 'Tax Compliance'.</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify 'Liability to Tax' and 'Tax Compliance' are visible</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>After navigating to News via the top nav, using the browser's back button must return to /wta/Information.</t>
+          <t>The category tree's default view must include the top-level categories 'Liability to Tax' and 'Tax Compliance'.</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Browser back correctly returned to https://regplus.kaz.com.bd/wta/Information.</t>
+          <t>Both expected top-level categories are visible in the default tree view.</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Browser back returns to /wta/Information</t>
+          <t>[PASS] 'Liability to Tax' and 'Tax Compliance' are both visible</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
@@ -2287,7 +2295,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>LANDING_31</t>
+          <t>LANDING_37</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2297,12 +2305,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Reloading the page preserves the authenticated session</t>
+          <t>Exactly 4 product tabs are present</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Reloading /wta/Information (F5) must keep the user authenticated and on the same page, not bounce them to the login page.</t>
+          <t>The product-tab row must show Workspace, World Tax Analyzer, Transfer Pricing Analyzer and RegBriefings - no more, no fewer.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2318,23 +2326,22 @@
       <c r="G32" s="2" t="inlineStr">
         <is>
           <t>1. Log in
-2. Reload the page
-3. Verify the user is still on /wta/Information, not redirected to /auth/login</t>
+2. Verify each of the 4 product tabs appears exactly once</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Reloading /wta/Information (F5) must keep the user authenticated and on the same page, not bounce them to the login page.</t>
+          <t>The product-tab row must show Workspace, World Tax Analyzer, Transfer Pricing Analyzer and RegBriefings - no more, no fewer.</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Reloading the page correctly preserved the authenticated session; still on https://regplus.kaz.com.bd/wta/Information.</t>
+          <t>Exactly the 4 expected product tabs are present.</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>[PASS] User remains on /wta/Information after reload (not redirected to login)</t>
+          <t>[PASS] Each of the 4 product tabs appears exactly once</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
@@ -2346,7 +2353,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>LANDING_32</t>
+          <t>LANDING_38</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2356,43 +2363,44 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>The content placeholder is shown before any selection</t>
+          <t>A single category can be checked without using 'Check All'</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Before selecting a jurisdiction or category, the right panel must show 'Select Jurisdictions and Categories'.</t>
+          <t>Clicking 'Liability to Tax's checkbox directly must check it, while 'Check All' remains unchecked (it only reflects when every category is checked). Note: the category LABEL text has no 'for' attribute linking it to its checkbox (confirmed live) - clicking the label is a no-op; only the checkbox input itself (or 'Check All', which has its own working handler) toggles selection.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on the landing page, nothing selected.</t>
+          <t>User is logged in and on the landing page.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Category: Liability to Tax</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
           <t>1. Log in
-2. Verify the 'Select Jurisdictions and Categories' placeholder is visible</t>
+2. Click 'Liability to Tax's checkbox
+3. Verify it is checked and 'Check All' remains unchecked</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Before selecting a jurisdiction or category, the right panel must show 'Select Jurisdictions and Categories'.</t>
+          <t>Clicking 'Liability to Tax's checkbox directly must check it, while 'Check All' remains unchecked (it only reflects when every category is checked). Note: the category LABEL text has no 'for' attribute linking it to its checkbox (confirmed live) - clicking the label is a no-op; only the checkbox input itself (or 'Check All', which has its own working handler) toggles selection.</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>The 'Select Jurisdictions and Categories' placeholder is correctly shown before any selection.</t>
+          <t>A single category can be selected independently of 'Check All'.</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Placeholder text is visible before any selection</t>
+          <t>[PASS] 'Liability to Tax' is checked while 'Check All' remains unchecked</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
@@ -2404,7 +2412,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>LANDING_33</t>
+          <t>LANDING_39</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2414,12 +2422,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Exactly 4 region tabs are present</t>
+          <t>Special-character input in the country search doesn't error</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>The jurisdiction panel must show exactly 4 region tabs: Asia Pacific, Americas, Europe, MEA - no more, no fewer.</t>
+          <t>Typing special characters into the country search box must be handled gracefully (the same 'No countries found...' empty state, no crash).</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2429,28 +2437,29 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Search term: @@@###$$$</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
           <t>1. Log in
-2. Verify exactly 4 region tabs are present</t>
+2. Type '@@@###$$$' into the country search box
+3. Verify the page does not error and shows the no-match message</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>The jurisdiction panel must show exactly 4 region tabs: Asia Pacific, Americas, Europe, MEA - no more, no fewer.</t>
+          <t>Typing special characters into the country search box must be handled gracefully (the same 'No countries found...' empty state, no crash).</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Exactly the 4 expected region tabs (Asia Pacific, Americas, Europe, MEA) are present.</t>
+          <t>Special-character input was handled gracefully with the expected empty-state message.</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Each of the 4 region tabs appears exactly once</t>
+          <t>[PASS] Special-character search shows the no-match message without breaking the panel</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
@@ -2462,7 +2471,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>LANDING_34</t>
+          <t>LANDING_40</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2472,44 +2481,44 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Asia Pacific region shows the expected number of countries</t>
+          <t>Special-character input in the category search doesn't error</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>The Asia Pacific region (default) must list 25 countries, confirmed live (Australia through Vietnam).</t>
+          <t>Typing special characters into the category search box must be handled gracefully (the same 'No results found.' empty state, no crash).</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on the landing page, Asia Pacific active.</t>
+          <t>User is logged in and on the landing page.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Search term: @@@###$$$</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
           <t>1. Log in
-2. Count the visible country checkboxes in the Asia Pacific list
-3. Verify the count is 25</t>
+2. Type '@@@###$$$' into the category search box
+3. Verify the page does not error and shows 'No results found.'</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>The Asia Pacific region (default) must list 25 countries, confirmed live (Australia through Vietnam).</t>
+          <t>Typing special characters into the category search box must be handled gracefully (the same 'No results found.' empty state, no crash).</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Asia Pacific correctly lists 25 countries.</t>
+          <t>Special-character input was handled gracefully with the expected empty-state message.</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Asia Pacific lists exactly 25 countries</t>
+          <t>[PASS] Special-character search shows 'No results found.' without breaking the panel</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
@@ -2521,7 +2530,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>LANDING_35</t>
+          <t>LANDING_41</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2531,17 +2540,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Exactly the 5 expected main nav items are present</t>
+          <t>'World Tax Analyzer' tab keeps the user within WTA</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>The top nav must show Information, Pillar 2, News, Forms and Regulations - no more, no fewer.</t>
+          <t>Clicking the already-active 'World Tax Analyzer' product tab must not navigate away from the WTA module.</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on the landing page.</t>
+          <t>User is logged in and on the landing page (WTA already active).</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2552,22 +2561,23 @@
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1. Log in
-2. Verify each of the 5 main nav items appears exactly once</t>
+2. Click the 'World Tax Analyzer' tab
+3. Verify the URL is still within /wta/</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>The top nav must show Information, Pillar 2, News, Forms and Regulations - no more, no fewer.</t>
+          <t>Clicking the already-active 'World Tax Analyzer' product tab must not navigate away from the WTA module.</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Exactly the 5 expected main nav items are present.</t>
+          <t>Clicking the already-active 'World Tax Analyzer' tab correctly kept the user within WTA, at https://regplusrc.reganalytics.com/wta/Information.</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Each of the 5 main nav items appears exactly once</t>
+          <t>[PASS] URL remains within /wta/ after clicking the already-active tab</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
@@ -2579,7 +2589,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>LANDING_36</t>
+          <t>LANDING_42</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2589,12 +2599,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Expected top-level categories are present in the tree</t>
+          <t>'Information' nav link points to /wta/Information</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>The category tree's default view must include the top-level categories 'Liability to Tax' and 'Tax Compliance'.</t>
+          <t>The 'Information' nav link's href must point to /wta/Information, consistent with it being the post-login landing page.</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2610,377 +2620,25 @@
       <c r="G37" s="2" t="inlineStr">
         <is>
           <t>1. Log in
-2. Verify 'Liability to Tax' and 'Tax Compliance' are visible</t>
+2. Verify the 'Information' nav link's href</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>The category tree's default view must include the top-level categories 'Liability to Tax' and 'Tax Compliance'.</t>
+          <t>The 'Information' nav link's href must point to /wta/Information, consistent with it being the post-login landing page.</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Both expected top-level categories are visible in the default tree view.</t>
+          <t>'Information' nav link correctly points to /wta/Information.</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>[PASS] 'Liability to Tax' and 'Tax Compliance' are both visible</t>
+          <t>[PASS] 'Information' nav link href contains /wta/Information</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>LANDING_37</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Exactly 4 product tabs are present</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>The product-tab row must show Workspace, World Tax Analyzer, Transfer Pricing Analyzer and RegBriefings - no more, no fewer.</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Verify each of the 4 product tabs appears exactly once</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>The product-tab row must show Workspace, World Tax Analyzer, Transfer Pricing Analyzer and RegBriefings - no more, no fewer.</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>Exactly the 4 expected product tabs are present.</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Each of the 4 product tabs appears exactly once</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>LANDING_38</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>A single category can be checked without using 'Check All'</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Liability to Tax's checkbox directly must check it, while 'Check All' remains unchecked (it only reflects when every category is checked). Note: the category LABEL text has no 'for' attribute linking it to its checkbox (confirmed live) - clicking the label is a no-op; only the checkbox input itself (or 'Check All', which has its own working handler) toggles selection.</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Category: Liability to Tax</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Click 'Liability to Tax's checkbox
-3. Verify it is checked and 'Check All' remains unchecked</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Liability to Tax's checkbox directly must check it, while 'Check All' remains unchecked (it only reflects when every category is checked). Note: the category LABEL text has no 'for' attribute linking it to its checkbox (confirmed live) - clicking the label is a no-op; only the checkbox input itself (or 'Check All', which has its own working handler) toggles selection.</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>A single category can be selected independently of 'Check All'.</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'Liability to Tax' is checked while 'Check All' remains unchecked</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>LANDING_39</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Special-character input in the country search doesn't error</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Typing special characters into the country search box must be handled gracefully (the same 'No countries found...' empty state, no crash).</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Search term: @@@###$$$</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Type '@@@###$$$' into the country search box
-3. Verify the page does not error and shows the no-match message</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Typing special characters into the country search box must be handled gracefully (the same 'No countries found...' empty state, no crash).</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Special-character input was handled gracefully with the expected empty-state message.</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Special-character search shows the no-match message without breaking the panel</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>LANDING_40</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Special-character input in the category search doesn't error</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Typing special characters into the category search box must be handled gracefully (the same 'No results found.' empty state, no crash).</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>Search term: @@@###$$$</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Type '@@@###$$$' into the category search box
-3. Verify the page does not error and shows 'No results found.'</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>Typing special characters into the category search box must be handled gracefully (the same 'No results found.' empty state, no crash).</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Special-character input was handled gracefully with the expected empty-state message.</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Special-character search shows 'No results found.' without breaking the panel</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>LANDING_41</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>'World Tax Analyzer' tab keeps the user within WTA</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Clicking the already-active 'World Tax Analyzer' product tab must not navigate away from the WTA module.</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page (WTA already active).</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Click the 'World Tax Analyzer' tab
-3. Verify the URL is still within /wta/</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Clicking the already-active 'World Tax Analyzer' product tab must not navigate away from the WTA module.</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>Clicking the already-active 'World Tax Analyzer' tab correctly kept the user within WTA, at https://regplus.kaz.com.bd/wta/Information.</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] URL remains within /wta/ after clicking the already-active tab</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>LANDING_42</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>'Information' nav link points to /wta/Information</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>The 'Information' nav link's href must point to /wta/Information, consistent with it being the post-login landing page.</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the landing page.</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Verify the 'Information' nav link's href</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>The 'Information' nav link's href must point to /wta/Information, consistent with it being the post-login landing page.</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>'Information' nav link correctly points to /wta/Information.</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'Information' nav link href contains /wta/Information</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/Dashboard/Dashboard_Test_Cases.xlsx
+++ b/test_data/Dashboard/Dashboard_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -537,7 +537,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Email: monir.smh@gmail.com / Password: &lt;masked&gt;</t>
+          <t>Email: nasimsaker@gmail.com / Password: &lt;masked&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>After login the app landed on https://regplus.reganalytics.com/wta/Information with the 'Jurisdictions and Categories' panel visible.</t>
+          <t>After login the app landed on https://regplusrc.reganalytics.com/wta/Information with the 'Jurisdictions and Categories' panel visible.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -563,6 +563,297 @@
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Top navigation and product tabs are visible</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>The main module nav (Information/News/Forms/Regulations) and the product tabs (Workspace/World Tax Analyzer/Transfer Pricing Analyzer/RegBriefings) must be visible on the landing page.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify each nav link and product tab is visible</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>The main module nav (Information/News/Forms/Regulations) and the product tabs (Workspace/World Tax Analyzer/Transfer Pricing Analyzer/RegBriefings) must be visible on the landing page.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>All main navigation links (Information, News, Forms, Regulations) and product tabs (Workspace, World Tax Analyzer, Transfer Pricing Analyzer, RegBriefings) are visible.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Information/News/Forms/Regulations links are visible
+[PASS] Workspace/World Tax Analyzer/Transfer Pricing Analyzer/RegBriefings tabs are visible</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_08</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>'Pillar 2' nav button is visible and enabled</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>The 'Pillar 2' dropdown trigger in the top nav must be visible and enabled. Its dropdown contents are covered in depth by the WTA Pillar2 Menu module - this is a light presence check only, to avoid duplicating that coverage.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify the 'Pillar 2' nav button is visible and enabled</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>The 'Pillar 2' dropdown trigger in the top nav must be visible and enabled. Its dropdown contents are covered in depth by the WTA Pillar2 Menu module - this is a light presence check only, to avoid duplicating that coverage.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>The 'Pillar 2' nav button is visible and enabled.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Pillar 2' nav button is visible and enabled</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_09</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>'Asia Pacific' region tab is selected by default</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>On first load, the 'Asia Pacific' region tab must carry the active/selected styling and 'Americas' must not.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify 'Asia Pacific' is the active region tab</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>On first load, the 'Asia Pacific' region tab must carry the active/selected styling and 'Americas' must not.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>'Asia Pacific' is the default active region tab.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Asia Pacific' is active and 'Americas' is not, by default</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_21</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>'Check All' (categories) is unchecked by default</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>On first load, the 'Check All' category checkbox must be unchecked.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify the 'Check All' checkbox is unchecked</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>On first load, the 'Check All' category checkbox must be unchecked.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>'Check All' is unchecked by default, as expected.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Check All' checkbox is unchecked by default</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>LANDING_32</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>The content placeholder is shown before any selection</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Before selecting a jurisdiction or category, the right panel must show 'Select Jurisdictions and Categories'.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the landing page, nothing selected.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Verify the 'Select Jurisdictions and Categories' placeholder is visible</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Before selecting a jurisdiction or category, the right panel must show 'Select Jurisdictions and Categories'.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>The 'Select Jurisdictions and Categories' placeholder is correctly shown before any selection.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Placeholder text is visible before any selection</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
